--- a/research/traditional_assets/database/data/tanzania/tanzania_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/tanzania/tanzania_construction_supplies.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1197846059198796</v>
+        <v>0.1194567521021199</v>
       </c>
       <c r="C2">
-        <v>269.5747770867852</v>
+        <v>267.3782753378715</v>
       </c>
       <c r="D2">
-        <v>211.2747770867852</v>
+        <v>211.7740253378715</v>
       </c>
       <c r="E2">
-        <v>-0.075</v>
+        <v>2.62075</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.69575</v>
       </c>
       <c r="G2">
         <v>58.3</v>
@@ -1445,28 +1445,28 @@
         <v>42.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.135596225</v>
       </c>
       <c r="N2">
-        <v>42.8</v>
+        <v>42.664403775</v>
       </c>
       <c r="O2">
-        <v>12.84</v>
+        <v>12.7993211325</v>
       </c>
       <c r="P2">
-        <v>29.96</v>
+        <v>29.8650826425</v>
       </c>
       <c r="Q2">
-        <v>37.26000000000001</v>
+        <v>37.1650826425</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1197846059198796</v>
+        <v>0.1203077293960808</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7205466882059816</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>315.6430055482739</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1194567521021199</v>
+        <v>0.1191288982843603</v>
       </c>
       <c r="C3">
-        <v>267.3782753378715</v>
+        <v>265.1841386530388</v>
       </c>
       <c r="D3">
-        <v>211.7740253378715</v>
+        <v>212.2756386530388</v>
       </c>
       <c r="E3">
-        <v>2.62075</v>
+        <v>5.3165</v>
       </c>
       <c r="F3">
-        <v>2.69575</v>
+        <v>5.3915</v>
       </c>
       <c r="G3">
         <v>58.3</v>
@@ -1527,28 +1527,28 @@
         <v>42.8</v>
       </c>
       <c r="M3">
-        <v>0.135596225</v>
+        <v>0.27119245</v>
       </c>
       <c r="N3">
-        <v>42.664403775</v>
+        <v>42.52880755</v>
       </c>
       <c r="O3">
-        <v>12.7993211325</v>
+        <v>12.758642265</v>
       </c>
       <c r="P3">
-        <v>29.8650826425</v>
+        <v>29.770165285</v>
       </c>
       <c r="Q3">
-        <v>37.1650826425</v>
+        <v>37.070165285</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1203077293960808</v>
+        <v>0.1208415288615922</v>
       </c>
       <c r="T3">
-        <v>0.7205466882059816</v>
+        <v>0.7257089370110108</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>315.6430055482739</v>
+        <v>157.821502774137</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1191288982843603</v>
+        <v>0.1188010444666007</v>
       </c>
       <c r="C4">
-        <v>265.1841386530388</v>
+        <v>262.9923838780404</v>
       </c>
       <c r="D4">
-        <v>212.2756386530388</v>
+        <v>212.7796338780404</v>
       </c>
       <c r="E4">
-        <v>5.3165</v>
+        <v>8.01225</v>
       </c>
       <c r="F4">
-        <v>5.3915</v>
+        <v>8.087249999999999</v>
       </c>
       <c r="G4">
         <v>58.3</v>
@@ -1609,28 +1609,28 @@
         <v>42.8</v>
       </c>
       <c r="M4">
-        <v>0.27119245</v>
+        <v>0.4067886749999999</v>
       </c>
       <c r="N4">
-        <v>42.52880755</v>
+        <v>42.393211325</v>
       </c>
       <c r="O4">
-        <v>12.758642265</v>
+        <v>12.7179633975</v>
       </c>
       <c r="P4">
-        <v>29.770165285</v>
+        <v>29.6752479275</v>
       </c>
       <c r="Q4">
-        <v>37.070165285</v>
+        <v>36.9752479275</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1208415288615922</v>
+        <v>0.1213863345016502</v>
       </c>
       <c r="T4">
-        <v>0.7257089370110108</v>
+        <v>0.7309776239357313</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>157.821502774137</v>
+        <v>105.214335182758</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1188010444666007</v>
+        <v>0.118473190648841</v>
       </c>
       <c r="C5">
-        <v>262.9923838780404</v>
+        <v>260.8030280189942</v>
       </c>
       <c r="D5">
-        <v>212.7796338780404</v>
+        <v>213.2860280189942</v>
       </c>
       <c r="E5">
-        <v>8.01225</v>
+        <v>10.708</v>
       </c>
       <c r="F5">
-        <v>8.087249999999999</v>
+        <v>10.783</v>
       </c>
       <c r="G5">
         <v>58.3</v>
@@ -1691,28 +1691,28 @@
         <v>42.8</v>
       </c>
       <c r="M5">
-        <v>0.4067886749999999</v>
+        <v>0.5423848999999999</v>
       </c>
       <c r="N5">
-        <v>42.393211325</v>
+        <v>42.2576151</v>
       </c>
       <c r="O5">
-        <v>12.7179633975</v>
+        <v>12.67728453</v>
       </c>
       <c r="P5">
-        <v>29.6752479275</v>
+        <v>29.58033057</v>
       </c>
       <c r="Q5">
-        <v>36.9752479275</v>
+        <v>36.88033057</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1213863345016502</v>
+        <v>0.1219424902592094</v>
       </c>
       <c r="T5">
-        <v>0.7309776239357313</v>
+        <v>0.7363560751713836</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>105.214335182758</v>
+        <v>78.91075138706849</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.118473190648841</v>
+        <v>0.1181453368310814</v>
       </c>
       <c r="C6">
-        <v>260.8030280189942</v>
+        <v>258.6160882442958</v>
       </c>
       <c r="D6">
-        <v>213.2860280189942</v>
+        <v>213.7948382442958</v>
       </c>
       <c r="E6">
-        <v>10.708</v>
+        <v>13.40375</v>
       </c>
       <c r="F6">
-        <v>10.783</v>
+        <v>13.47875</v>
       </c>
       <c r="G6">
         <v>58.3</v>
@@ -1773,28 +1773,28 @@
         <v>42.8</v>
       </c>
       <c r="M6">
-        <v>0.5423848999999999</v>
+        <v>0.677981125</v>
       </c>
       <c r="N6">
-        <v>42.2576151</v>
+        <v>42.12201887499999</v>
       </c>
       <c r="O6">
-        <v>12.67728453</v>
+        <v>12.6366056625</v>
       </c>
       <c r="P6">
-        <v>29.58033057</v>
+        <v>29.4854132125</v>
       </c>
       <c r="Q6">
-        <v>36.88033057</v>
+        <v>36.7854132125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1219424902592094</v>
+        <v>0.1225103545590331</v>
       </c>
       <c r="T6">
-        <v>0.7363560751713836</v>
+        <v>0.7418477569593653</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>78.91075138706849</v>
+        <v>63.12860110965478</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1181453368310814</v>
+        <v>0.1178174830133218</v>
       </c>
       <c r="C7">
-        <v>258.6160882442958</v>
+        <v>256.4315818865587</v>
       </c>
       <c r="D7">
-        <v>213.7948382442958</v>
+        <v>214.3060818865587</v>
       </c>
       <c r="E7">
-        <v>13.40375</v>
+        <v>16.0995</v>
       </c>
       <c r="F7">
-        <v>13.47875</v>
+        <v>16.1745</v>
       </c>
       <c r="G7">
         <v>58.3</v>
@@ -1855,28 +1855,28 @@
         <v>42.8</v>
       </c>
       <c r="M7">
-        <v>0.677981125</v>
+        <v>0.8135773500000001</v>
       </c>
       <c r="N7">
-        <v>42.12201887499999</v>
+        <v>41.98642264999999</v>
       </c>
       <c r="O7">
-        <v>12.6366056625</v>
+        <v>12.595926795</v>
       </c>
       <c r="P7">
-        <v>29.4854132125</v>
+        <v>29.390495855</v>
       </c>
       <c r="Q7">
-        <v>36.7854132125</v>
+        <v>36.690495855</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1225103545590331</v>
+        <v>0.1230903010780019</v>
       </c>
       <c r="T7">
-        <v>0.7418477569593653</v>
+        <v>0.7474562830407084</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>63.12860110965478</v>
+        <v>52.60716759137897</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1178174830133218</v>
+        <v>0.1174896291955621</v>
       </c>
       <c r="C8">
-        <v>256.4315818865587</v>
+        <v>254.2495264445822</v>
       </c>
       <c r="D8">
-        <v>214.3060818865587</v>
+        <v>214.8197764445822</v>
       </c>
       <c r="E8">
-        <v>16.0995</v>
+        <v>18.79525</v>
       </c>
       <c r="F8">
-        <v>16.1745</v>
+        <v>18.87025</v>
       </c>
       <c r="G8">
         <v>58.3</v>
@@ -1937,28 +1937,28 @@
         <v>42.8</v>
       </c>
       <c r="M8">
-        <v>0.8135773499999999</v>
+        <v>0.9491735749999999</v>
       </c>
       <c r="N8">
-        <v>41.98642264999999</v>
+        <v>41.85082642499999</v>
       </c>
       <c r="O8">
-        <v>12.595926795</v>
+        <v>12.5552479275</v>
       </c>
       <c r="P8">
-        <v>29.390495855</v>
+        <v>29.2955784975</v>
       </c>
       <c r="Q8">
-        <v>36.690495855</v>
+        <v>36.5955784975</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1230903010780019</v>
+        <v>0.1236827195651206</v>
       </c>
       <c r="T8">
-        <v>0.7474562830407084</v>
+        <v>0.7531854225861665</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>52.60716759137899</v>
+        <v>45.0918579354677</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1174896291955621</v>
+        <v>0.1171617753778025</v>
       </c>
       <c r="C9">
-        <v>254.2495264445822</v>
+        <v>252.0699395853485</v>
       </c>
       <c r="D9">
-        <v>214.8197764445822</v>
+        <v>215.3359395853485</v>
       </c>
       <c r="E9">
-        <v>18.79525</v>
+        <v>21.491</v>
       </c>
       <c r="F9">
-        <v>18.87025</v>
+        <v>21.566</v>
       </c>
       <c r="G9">
         <v>58.3</v>
@@ -2019,28 +2019,28 @@
         <v>42.8</v>
       </c>
       <c r="M9">
-        <v>0.9491735750000001</v>
+        <v>1.0847698</v>
       </c>
       <c r="N9">
-        <v>41.85082642499999</v>
+        <v>41.7152302</v>
       </c>
       <c r="O9">
-        <v>12.5552479275</v>
+        <v>12.51456906</v>
       </c>
       <c r="P9">
-        <v>29.2955784975</v>
+        <v>29.20066114</v>
       </c>
       <c r="Q9">
-        <v>36.5955784975</v>
+        <v>36.50066114000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1236827195651206</v>
+        <v>0.1242880167150027</v>
       </c>
       <c r="T9">
-        <v>0.7531854225861665</v>
+        <v>0.7590391086434822</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.09185793546769</v>
+        <v>39.45537569353424</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1171617753778025</v>
+        <v>0.1168339215600429</v>
       </c>
       <c r="C10">
-        <v>252.0699395853485</v>
+        <v>249.8928391460474</v>
       </c>
       <c r="D10">
-        <v>215.3359395853485</v>
+        <v>215.8545891460474</v>
       </c>
       <c r="E10">
-        <v>21.491</v>
+        <v>24.18675</v>
       </c>
       <c r="F10">
-        <v>21.566</v>
+        <v>24.26175</v>
       </c>
       <c r="G10">
         <v>58.3</v>
@@ -2101,28 +2101,28 @@
         <v>42.8</v>
       </c>
       <c r="M10">
-        <v>1.0847698</v>
+        <v>1.220366025</v>
       </c>
       <c r="N10">
-        <v>41.7152302</v>
+        <v>41.579633975</v>
       </c>
       <c r="O10">
-        <v>12.51456906</v>
+        <v>12.4738901925</v>
       </c>
       <c r="P10">
-        <v>29.20066114</v>
+        <v>29.1057437825</v>
       </c>
       <c r="Q10">
-        <v>36.50066114000001</v>
+        <v>36.4057437825</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1242880167150027</v>
+        <v>0.1249066170989482</v>
       </c>
       <c r="T10">
-        <v>0.7590391086434822</v>
+        <v>0.7650214471416181</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.45537569353424</v>
+        <v>35.07144506091933</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1168339215600429</v>
+        <v>0.1165060677422832</v>
       </c>
       <c r="C11">
-        <v>249.8928391460474</v>
+        <v>247.7182431361319</v>
       </c>
       <c r="D11">
-        <v>215.8545891460474</v>
+        <v>216.3757431361319</v>
       </c>
       <c r="E11">
-        <v>24.18675</v>
+        <v>26.8825</v>
       </c>
       <c r="F11">
-        <v>24.26175</v>
+        <v>26.9575</v>
       </c>
       <c r="G11">
         <v>58.3</v>
@@ -2183,28 +2183,28 @@
         <v>42.8</v>
       </c>
       <c r="M11">
-        <v>1.220366025</v>
+        <v>1.35596225</v>
       </c>
       <c r="N11">
-        <v>41.579633975</v>
+        <v>41.44403775</v>
       </c>
       <c r="O11">
-        <v>12.4738901925</v>
+        <v>12.433211325</v>
       </c>
       <c r="P11">
-        <v>29.1057437825</v>
+        <v>29.010826425</v>
       </c>
       <c r="Q11">
-        <v>36.4057437825</v>
+        <v>36.310826425</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1249066170989482</v>
+        <v>0.1255389641580924</v>
       </c>
       <c r="T11">
-        <v>0.7650214471416181</v>
+        <v>0.7711367264952681</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.07144506091933</v>
+        <v>31.5643005548274</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1165060677422832</v>
+        <v>0.1161782139245236</v>
       </c>
       <c r="C12">
-        <v>247.7182431361319</v>
+        <v>245.5461697394015</v>
       </c>
       <c r="D12">
-        <v>216.3757431361319</v>
+        <v>216.8994197394015</v>
       </c>
       <c r="E12">
-        <v>26.8825</v>
+        <v>29.57825</v>
       </c>
       <c r="F12">
-        <v>26.9575</v>
+        <v>29.65325</v>
       </c>
       <c r="G12">
         <v>58.3</v>
@@ -2265,28 +2265,28 @@
         <v>42.8</v>
       </c>
       <c r="M12">
-        <v>1.35596225</v>
+        <v>1.491558475</v>
       </c>
       <c r="N12">
-        <v>41.44403775</v>
+        <v>41.308441525</v>
       </c>
       <c r="O12">
-        <v>12.433211325</v>
+        <v>12.3925324575</v>
       </c>
       <c r="P12">
-        <v>29.010826425</v>
+        <v>28.9159090675</v>
       </c>
       <c r="Q12">
-        <v>36.310826425</v>
+        <v>36.21590906750001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1255389641580924</v>
+        <v>0.1261855212635096</v>
       </c>
       <c r="T12">
-        <v>0.7711367264952681</v>
+        <v>0.7773894278568653</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.56430055482739</v>
+        <v>28.69481868620672</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1161782139245236</v>
+        <v>0.1158503601067639</v>
       </c>
       <c r="C13">
-        <v>245.5461697394015</v>
+        <v>243.3766373161186</v>
       </c>
       <c r="D13">
-        <v>216.8994197394015</v>
+        <v>217.4256373161186</v>
       </c>
       <c r="E13">
-        <v>29.57825</v>
+        <v>32.27399999999999</v>
       </c>
       <c r="F13">
-        <v>29.65325</v>
+        <v>32.349</v>
       </c>
       <c r="G13">
         <v>58.3</v>
@@ -2347,28 +2347,28 @@
         <v>42.8</v>
       </c>
       <c r="M13">
-        <v>1.491558475</v>
+        <v>1.6271547</v>
       </c>
       <c r="N13">
-        <v>41.308441525</v>
+        <v>41.1728453</v>
       </c>
       <c r="O13">
-        <v>12.3925324575</v>
+        <v>12.35185359</v>
       </c>
       <c r="P13">
-        <v>28.9159090675</v>
+        <v>28.82099171</v>
       </c>
       <c r="Q13">
-        <v>36.21590906750001</v>
+        <v>36.12099171000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1261855212635096</v>
+        <v>0.1268467728485954</v>
       </c>
       <c r="T13">
-        <v>0.7773894278568653</v>
+        <v>0.7837842360675897</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.69481868620672</v>
+        <v>26.3035837956895</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1158503601067639</v>
+        <v>0.1155225062890043</v>
       </c>
       <c r="C14">
-        <v>243.3766373161186</v>
+        <v>241.2096644051531</v>
       </c>
       <c r="D14">
-        <v>217.4256373161186</v>
+        <v>217.9544144051531</v>
       </c>
       <c r="E14">
-        <v>32.27399999999999</v>
+        <v>34.96975</v>
       </c>
       <c r="F14">
-        <v>32.349</v>
+        <v>35.04475</v>
       </c>
       <c r="G14">
         <v>58.3</v>
@@ -2429,28 +2429,28 @@
         <v>42.8</v>
       </c>
       <c r="M14">
-        <v>1.6271547</v>
+        <v>1.762750925</v>
       </c>
       <c r="N14">
-        <v>41.1728453</v>
+        <v>41.037249075</v>
       </c>
       <c r="O14">
-        <v>12.35185359</v>
+        <v>12.3111747225</v>
       </c>
       <c r="P14">
-        <v>28.82099171</v>
+        <v>28.7260743525</v>
       </c>
       <c r="Q14">
-        <v>36.12099171000001</v>
+        <v>36.0260743525</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1268467728485954</v>
+        <v>0.1275232256195452</v>
       </c>
       <c r="T14">
-        <v>0.7837842360675897</v>
+        <v>0.7903260513636182</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.3035837956895</v>
+        <v>24.28023119602107</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1155225062890043</v>
+        <v>0.1151946524712446</v>
       </c>
       <c r="C15">
-        <v>241.2096644051531</v>
+        <v>239.0452697261601</v>
       </c>
       <c r="D15">
-        <v>217.9544144051531</v>
+        <v>218.4857697261601</v>
       </c>
       <c r="E15">
-        <v>34.96975</v>
+        <v>37.6655</v>
       </c>
       <c r="F15">
-        <v>35.04475</v>
+        <v>37.7405</v>
       </c>
       <c r="G15">
         <v>58.3</v>
@@ -2511,28 +2511,28 @@
         <v>42.8</v>
       </c>
       <c r="M15">
-        <v>1.762750925</v>
+        <v>1.89834715</v>
       </c>
       <c r="N15">
-        <v>41.037249075</v>
+        <v>40.90165285</v>
       </c>
       <c r="O15">
-        <v>12.3111747225</v>
+        <v>12.270495855</v>
       </c>
       <c r="P15">
-        <v>28.7260743525</v>
+        <v>28.631156995</v>
       </c>
       <c r="Q15">
-        <v>36.0260743525</v>
+        <v>35.931156995</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1275232256195452</v>
+        <v>0.1282154098502845</v>
       </c>
       <c r="T15">
-        <v>0.7903260513636182</v>
+        <v>0.7970200018990892</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.28023119602107</v>
+        <v>22.54592896773385</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1151946524712446</v>
+        <v>0.114866798653485</v>
       </c>
       <c r="C16">
-        <v>239.0452697261601</v>
+        <v>236.8834721817889</v>
       </c>
       <c r="D16">
-        <v>218.4857697261601</v>
+        <v>219.0197221817889</v>
       </c>
       <c r="E16">
-        <v>37.6655</v>
+        <v>40.36125</v>
       </c>
       <c r="F16">
-        <v>37.7405</v>
+        <v>40.43625</v>
       </c>
       <c r="G16">
         <v>58.3</v>
@@ -2593,28 +2593,28 @@
         <v>42.8</v>
       </c>
       <c r="M16">
-        <v>1.89834715</v>
+        <v>2.033943375</v>
       </c>
       <c r="N16">
-        <v>40.90165285</v>
+        <v>40.766056625</v>
       </c>
       <c r="O16">
-        <v>12.270495855</v>
+        <v>12.2298169875</v>
       </c>
       <c r="P16">
-        <v>28.631156995</v>
+        <v>28.5362396375</v>
       </c>
       <c r="Q16">
-        <v>35.931156995</v>
+        <v>35.8362396375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1282154098502845</v>
+        <v>0.1289238807688059</v>
       </c>
       <c r="T16">
-        <v>0.7970200018990892</v>
+        <v>0.8038714571530418</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.54592896773385</v>
+        <v>21.04286703655159</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.114866798653485</v>
+        <v>0.1145389448357254</v>
       </c>
       <c r="C17">
-        <v>236.8834721817889</v>
+        <v>234.7242908599245</v>
       </c>
       <c r="D17">
-        <v>219.0197221817889</v>
+        <v>219.5562908599244</v>
       </c>
       <c r="E17">
-        <v>40.36124999999999</v>
+        <v>43.057</v>
       </c>
       <c r="F17">
-        <v>40.43624999999999</v>
+        <v>43.132</v>
       </c>
       <c r="G17">
         <v>58.3</v>
@@ -2675,28 +2675,28 @@
         <v>42.8</v>
       </c>
       <c r="M17">
-        <v>2.033943375</v>
+        <v>2.1695396</v>
       </c>
       <c r="N17">
-        <v>40.766056625</v>
+        <v>40.6304604</v>
       </c>
       <c r="O17">
-        <v>12.2298169875</v>
+        <v>12.18913812</v>
       </c>
       <c r="P17">
-        <v>28.5362396375</v>
+        <v>28.44132228</v>
       </c>
       <c r="Q17">
-        <v>35.8362396375</v>
+        <v>35.74132228000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1289238807688059</v>
+        <v>0.1296492200425302</v>
       </c>
       <c r="T17">
-        <v>0.8038714571530418</v>
+        <v>0.8108860422939933</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.04286703655159</v>
+        <v>19.72768784676712</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1145389448357254</v>
+        <v>0.1142110910179657</v>
       </c>
       <c r="C18">
-        <v>234.7242908599245</v>
+        <v>232.5677450359622</v>
       </c>
       <c r="D18">
-        <v>219.5562908599244</v>
+        <v>220.0954950359622</v>
       </c>
       <c r="E18">
-        <v>43.057</v>
+        <v>45.75275</v>
       </c>
       <c r="F18">
-        <v>43.132</v>
+        <v>45.82775</v>
       </c>
       <c r="G18">
         <v>58.3</v>
@@ -2757,28 +2757,28 @@
         <v>42.8</v>
       </c>
       <c r="M18">
-        <v>2.1695396</v>
+        <v>2.305135825</v>
       </c>
       <c r="N18">
-        <v>40.6304604</v>
+        <v>40.494864175</v>
       </c>
       <c r="O18">
-        <v>12.18913812</v>
+        <v>12.1484592525</v>
       </c>
       <c r="P18">
-        <v>28.44132228</v>
+        <v>28.3464049225</v>
       </c>
       <c r="Q18">
-        <v>35.74132228000001</v>
+        <v>35.6464049225</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1296492200425302</v>
+        <v>0.130392037371043</v>
       </c>
       <c r="T18">
-        <v>0.8108860422939933</v>
+        <v>0.8180696535829196</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.72768784676712</v>
+        <v>18.5672356204867</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1142110910179657</v>
+        <v>0.1138832372002061</v>
       </c>
       <c r="C19">
-        <v>232.5677450359622</v>
+        <v>230.4138541751159</v>
       </c>
       <c r="D19">
-        <v>220.0954950359622</v>
+        <v>220.6373541751159</v>
       </c>
       <c r="E19">
-        <v>45.75275</v>
+        <v>48.4485</v>
       </c>
       <c r="F19">
-        <v>45.82775</v>
+        <v>48.52350000000001</v>
       </c>
       <c r="G19">
         <v>58.3</v>
@@ -2839,28 +2839,28 @@
         <v>42.8</v>
       </c>
       <c r="M19">
-        <v>2.305135825</v>
+        <v>2.44073205</v>
       </c>
       <c r="N19">
-        <v>40.494864175</v>
+        <v>40.35926795</v>
       </c>
       <c r="O19">
-        <v>12.1484592525</v>
+        <v>12.107780385</v>
       </c>
       <c r="P19">
-        <v>28.3464049225</v>
+        <v>28.251487565</v>
       </c>
       <c r="Q19">
-        <v>35.6464049225</v>
+        <v>35.551487565</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.130392037371043</v>
+        <v>0.1311529721953733</v>
       </c>
       <c r="T19">
-        <v>0.8180696535829196</v>
+        <v>0.825428474903283</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.5672356204867</v>
+        <v>17.53572253045966</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1138832372002061</v>
+        <v>0.1135553833824465</v>
       </c>
       <c r="C20">
-        <v>230.4138541751159</v>
+        <v>228.2626379347603</v>
       </c>
       <c r="D20">
-        <v>220.6373541751159</v>
+        <v>221.1818879347603</v>
       </c>
       <c r="E20">
-        <v>48.4485</v>
+        <v>51.14424999999999</v>
       </c>
       <c r="F20">
-        <v>48.5235</v>
+        <v>51.21925</v>
       </c>
       <c r="G20">
         <v>58.3</v>
@@ -2921,28 +2921,28 @@
         <v>42.8</v>
       </c>
       <c r="M20">
-        <v>2.44073205</v>
+        <v>2.576328275</v>
       </c>
       <c r="N20">
-        <v>40.35926795</v>
+        <v>40.223671725</v>
       </c>
       <c r="O20">
-        <v>12.107780385</v>
+        <v>12.0671015175</v>
       </c>
       <c r="P20">
-        <v>28.251487565</v>
+        <v>28.1565702075</v>
       </c>
       <c r="Q20">
-        <v>35.551487565</v>
+        <v>35.4565702075</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1311529721953733</v>
+        <v>0.1319326955338845</v>
       </c>
       <c r="T20">
-        <v>0.825428474903283</v>
+        <v>0.8329689955155072</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.53572253045966</v>
+        <v>16.61278976569863</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1135553833824465</v>
+        <v>0.1132275295646868</v>
       </c>
       <c r="C21">
-        <v>228.2626379347603</v>
+        <v>226.1141161668081</v>
       </c>
       <c r="D21">
-        <v>221.1818879347603</v>
+        <v>221.7291161668081</v>
       </c>
       <c r="E21">
-        <v>51.14424999999999</v>
+        <v>53.84</v>
       </c>
       <c r="F21">
-        <v>51.21925</v>
+        <v>53.915</v>
       </c>
       <c r="G21">
         <v>58.3</v>
@@ -3003,28 +3003,28 @@
         <v>42.8</v>
       </c>
       <c r="M21">
-        <v>2.576328275</v>
+        <v>2.7119245</v>
       </c>
       <c r="N21">
-        <v>40.223671725</v>
+        <v>40.0880755</v>
       </c>
       <c r="O21">
-        <v>12.0671015175</v>
+        <v>12.02642265</v>
       </c>
       <c r="P21">
-        <v>28.1565702075</v>
+        <v>28.06165284999999</v>
       </c>
       <c r="Q21">
-        <v>35.4565702075</v>
+        <v>35.36165285</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1319326955338845</v>
+        <v>0.1327319119558585</v>
       </c>
       <c r="T21">
-        <v>0.8329689955155072</v>
+        <v>0.8406980291430372</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.61278976569863</v>
+        <v>15.7821502774137</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1132275295646868</v>
+        <v>0.1128996757469272</v>
       </c>
       <c r="C22">
-        <v>226.1141161668081</v>
+        <v>223.9683089201223</v>
       </c>
       <c r="D22">
-        <v>221.7291161668081</v>
+        <v>222.2790589201223</v>
       </c>
       <c r="E22">
-        <v>53.84</v>
+        <v>56.53575</v>
       </c>
       <c r="F22">
-        <v>53.915</v>
+        <v>56.61075</v>
       </c>
       <c r="G22">
         <v>58.3</v>
@@ -3085,28 +3085,28 @@
         <v>42.8</v>
       </c>
       <c r="M22">
-        <v>2.7119245</v>
+        <v>2.847520725</v>
       </c>
       <c r="N22">
-        <v>40.0880755</v>
+        <v>39.95247927499999</v>
       </c>
       <c r="O22">
-        <v>12.02642265</v>
+        <v>11.9857437825</v>
       </c>
       <c r="P22">
-        <v>28.06165284999999</v>
+        <v>27.9667354925</v>
       </c>
       <c r="Q22">
-        <v>35.36165285</v>
+        <v>35.2667354925</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1327319119558585</v>
+        <v>0.1335513617049711</v>
       </c>
       <c r="T22">
-        <v>0.8406980291430372</v>
+        <v>0.848622734507973</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.7821502774137</v>
+        <v>15.03061931182257</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1128996757469272</v>
+        <v>0.1125718219291676</v>
       </c>
       <c r="C23">
-        <v>223.9683089201224</v>
+        <v>221.8252364429653</v>
       </c>
       <c r="D23">
-        <v>222.2790589201224</v>
+        <v>222.8317364429653</v>
       </c>
       <c r="E23">
-        <v>56.53574999999999</v>
+        <v>59.2315</v>
       </c>
       <c r="F23">
-        <v>56.61075</v>
+        <v>59.3065</v>
       </c>
       <c r="G23">
         <v>58.3</v>
@@ -3167,28 +3167,28 @@
         <v>42.8</v>
       </c>
       <c r="M23">
-        <v>2.847520725</v>
+        <v>2.98311695</v>
       </c>
       <c r="N23">
-        <v>39.95247927499999</v>
+        <v>39.81688304999999</v>
       </c>
       <c r="O23">
-        <v>11.9857437825</v>
+        <v>11.945064915</v>
       </c>
       <c r="P23">
-        <v>27.9667354925</v>
+        <v>27.871818135</v>
       </c>
       <c r="Q23">
-        <v>35.2667354925</v>
+        <v>35.171818135</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1335513617049711</v>
+        <v>0.1343918229861122</v>
       </c>
       <c r="T23">
-        <v>0.8486227345079728</v>
+        <v>0.8567506374463685</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.03061931182257</v>
+        <v>14.34740934310336</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1125718219291676</v>
+        <v>0.1122439681114079</v>
       </c>
       <c r="C24">
-        <v>221.8252364429653</v>
+        <v>219.6849191854835</v>
       </c>
       <c r="D24">
-        <v>222.8317364429653</v>
+        <v>223.3871691854835</v>
       </c>
       <c r="E24">
-        <v>59.2315</v>
+        <v>61.92724999999999</v>
       </c>
       <c r="F24">
-        <v>59.3065</v>
+        <v>62.00225</v>
       </c>
       <c r="G24">
         <v>58.3</v>
@@ -3249,28 +3249,28 @@
         <v>42.8</v>
       </c>
       <c r="M24">
-        <v>2.98311695</v>
+        <v>3.118713174999999</v>
       </c>
       <c r="N24">
-        <v>39.81688304999999</v>
+        <v>39.681286825</v>
       </c>
       <c r="O24">
-        <v>11.945064915</v>
+        <v>11.9043860475</v>
       </c>
       <c r="P24">
-        <v>27.871818135</v>
+        <v>27.7769007775</v>
       </c>
       <c r="Q24">
-        <v>35.171818135</v>
+        <v>35.07690077750001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1343918229861122</v>
+        <v>0.1352541144303999</v>
       </c>
       <c r="T24">
-        <v>0.8567506374463685</v>
+        <v>0.8650896547468002</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.34740934310336</v>
+        <v>13.72360893688148</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1122439681114079</v>
+        <v>0.1119161142936483</v>
       </c>
       <c r="C25">
-        <v>219.6849191854835</v>
+        <v>217.5473778022295</v>
       </c>
       <c r="D25">
-        <v>223.3871691854835</v>
+        <v>223.9453778022295</v>
       </c>
       <c r="E25">
-        <v>61.92724999999999</v>
+        <v>64.623</v>
       </c>
       <c r="F25">
-        <v>62.00225</v>
+        <v>64.69800000000001</v>
       </c>
       <c r="G25">
         <v>58.3</v>
@@ -3331,28 +3331,28 @@
         <v>42.8</v>
       </c>
       <c r="M25">
-        <v>3.118713174999999</v>
+        <v>3.2543094</v>
       </c>
       <c r="N25">
-        <v>39.681286825</v>
+        <v>39.5456906</v>
       </c>
       <c r="O25">
-        <v>11.9043860475</v>
+        <v>11.86370718</v>
       </c>
       <c r="P25">
-        <v>27.7769007775</v>
+        <v>27.68198342</v>
       </c>
       <c r="Q25">
-        <v>35.07690077750001</v>
+        <v>34.98198342000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1352541144303999</v>
+        <v>0.1361390977548003</v>
       </c>
       <c r="T25">
-        <v>0.8650896547468002</v>
+        <v>0.8736481198709277</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.72360893688148</v>
+        <v>13.15179189784475</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1119161142936483</v>
+        <v>0.1118507604758886</v>
       </c>
       <c r="C26">
-        <v>217.5473778022296</v>
+        <v>214.9632337948083</v>
       </c>
       <c r="D26">
-        <v>223.9453778022295</v>
+        <v>224.0569837948083</v>
       </c>
       <c r="E26">
-        <v>64.62299999999999</v>
+        <v>67.31874999999999</v>
       </c>
       <c r="F26">
-        <v>64.69799999999999</v>
+        <v>67.39375</v>
       </c>
       <c r="G26">
         <v>58.3</v>
@@ -3413,45 +3413,45 @@
         <v>42.8</v>
       </c>
       <c r="M26">
-        <v>3.254309399999999</v>
+        <v>3.49099625</v>
       </c>
       <c r="N26">
-        <v>39.5456906</v>
+        <v>39.30900375</v>
       </c>
       <c r="O26">
-        <v>11.86370718</v>
+        <v>11.792701125</v>
       </c>
       <c r="P26">
-        <v>27.68198342</v>
+        <v>27.51630262499999</v>
       </c>
       <c r="Q26">
-        <v>34.98198342000001</v>
+        <v>34.816302625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1361390977548003</v>
+        <v>0.1370476806345182</v>
       </c>
       <c r="T26">
-        <v>0.8736481198709277</v>
+        <v>0.8824348107316986</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.15179189784475</v>
+        <v>12.26011056299473</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1118507604758886</v>
+        <v>0.111533406658129</v>
       </c>
       <c r="C27">
-        <v>214.9632337948083</v>
+        <v>212.8110205709922</v>
       </c>
       <c r="D27">
-        <v>224.0569837948083</v>
+        <v>224.6005205709922</v>
       </c>
       <c r="E27">
-        <v>67.31874999999999</v>
+        <v>70.0145</v>
       </c>
       <c r="F27">
-        <v>67.39375</v>
+        <v>70.0895</v>
       </c>
       <c r="G27">
         <v>58.3</v>
@@ -3495,28 +3495,28 @@
         <v>42.8</v>
       </c>
       <c r="M27">
-        <v>3.49099625</v>
+        <v>3.6306361</v>
       </c>
       <c r="N27">
-        <v>39.30900375</v>
+        <v>39.1693639</v>
       </c>
       <c r="O27">
-        <v>11.792701125</v>
+        <v>11.75080917</v>
       </c>
       <c r="P27">
-        <v>27.51630262499999</v>
+        <v>27.41855473</v>
       </c>
       <c r="Q27">
-        <v>34.816302625</v>
+        <v>34.71855473000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1370476806345182</v>
+        <v>0.1379808198082824</v>
       </c>
       <c r="T27">
-        <v>0.8824348107316986</v>
+        <v>0.8914589797238416</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.26011056299473</v>
+        <v>11.7885678490334</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.111533406658129</v>
+        <v>0.1112160528403693</v>
       </c>
       <c r="C28">
-        <v>212.8110205709922</v>
+        <v>210.6614508769592</v>
       </c>
       <c r="D28">
-        <v>224.6005205709922</v>
+        <v>225.1467008769593</v>
       </c>
       <c r="E28">
-        <v>70.0145</v>
+        <v>72.71025</v>
       </c>
       <c r="F28">
-        <v>70.0895</v>
+        <v>72.78525</v>
       </c>
       <c r="G28">
         <v>58.3</v>
@@ -3577,28 +3577,28 @@
         <v>42.8</v>
       </c>
       <c r="M28">
-        <v>3.6306361</v>
+        <v>3.77027595</v>
       </c>
       <c r="N28">
-        <v>39.1693639</v>
+        <v>39.02972405</v>
       </c>
       <c r="O28">
-        <v>11.75080917</v>
+        <v>11.708917215</v>
       </c>
       <c r="P28">
-        <v>27.41855473</v>
+        <v>27.320806835</v>
       </c>
       <c r="Q28">
-        <v>34.71855473000001</v>
+        <v>34.620806835</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1379808198082824</v>
+        <v>0.1389395244388621</v>
       </c>
       <c r="T28">
-        <v>0.8914589797238416</v>
+        <v>0.9007303862226187</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.7885678490334</v>
+        <v>11.35195422499512</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1112160528403693</v>
+        <v>0.1108986990226097</v>
       </c>
       <c r="C29">
-        <v>210.6614508769592</v>
+        <v>208.5145440452147</v>
       </c>
       <c r="D29">
-        <v>225.1467008769593</v>
+        <v>225.6955440452147</v>
       </c>
       <c r="E29">
-        <v>72.71025</v>
+        <v>75.40600000000001</v>
       </c>
       <c r="F29">
-        <v>72.78525</v>
+        <v>75.48100000000001</v>
       </c>
       <c r="G29">
         <v>58.3</v>
@@ -3659,28 +3659,28 @@
         <v>42.8</v>
       </c>
       <c r="M29">
-        <v>3.77027595</v>
+        <v>3.9099158</v>
       </c>
       <c r="N29">
-        <v>39.02972405</v>
+        <v>38.8900842</v>
       </c>
       <c r="O29">
-        <v>11.708917215</v>
+        <v>11.66702526</v>
       </c>
       <c r="P29">
-        <v>27.320806835</v>
+        <v>27.22305894</v>
       </c>
       <c r="Q29">
-        <v>34.620806835</v>
+        <v>34.52305894</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1389395244388621</v>
+        <v>0.1399248597536246</v>
       </c>
       <c r="T29">
-        <v>0.9007303862226187</v>
+        <v>0.9102593317908061</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.35195422499512</v>
+        <v>10.94652728838815</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1108986990226097</v>
+        <v>0.1105813452048501</v>
       </c>
       <c r="C30">
-        <v>208.5145440452147</v>
+        <v>206.370319597233</v>
       </c>
       <c r="D30">
-        <v>225.6955440452147</v>
+        <v>226.247069597233</v>
       </c>
       <c r="E30">
-        <v>75.40600000000001</v>
+        <v>78.10175000000001</v>
       </c>
       <c r="F30">
-        <v>75.48100000000001</v>
+        <v>78.17675000000001</v>
       </c>
       <c r="G30">
         <v>58.3</v>
@@ -3741,28 +3741,28 @@
         <v>42.8</v>
       </c>
       <c r="M30">
-        <v>3.9099158</v>
+        <v>4.04955565</v>
       </c>
       <c r="N30">
-        <v>38.8900842</v>
+        <v>38.75044435</v>
       </c>
       <c r="O30">
-        <v>11.66702526</v>
+        <v>11.625133305</v>
       </c>
       <c r="P30">
-        <v>27.22305894</v>
+        <v>27.125311045</v>
       </c>
       <c r="Q30">
-        <v>34.52305894</v>
+        <v>34.425311045</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1399248597536246</v>
+        <v>0.1409379509927466</v>
       </c>
       <c r="T30">
-        <v>0.9102593317908061</v>
+        <v>0.9200566983609145</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.94652728838815</v>
+        <v>10.56906083016787</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1105813452048501</v>
+        <v>0.1102639913870904</v>
       </c>
       <c r="C31">
-        <v>206.370319597233</v>
+        <v>204.2287972457722</v>
       </c>
       <c r="D31">
-        <v>226.247069597233</v>
+        <v>226.8012972457722</v>
       </c>
       <c r="E31">
-        <v>78.10175</v>
+        <v>80.79749999999999</v>
       </c>
       <c r="F31">
-        <v>78.17675</v>
+        <v>80.87249999999999</v>
       </c>
       <c r="G31">
         <v>58.3</v>
@@ -3823,28 +3823,28 @@
         <v>42.8</v>
       </c>
       <c r="M31">
-        <v>4.049555649999999</v>
+        <v>4.189195499999999</v>
       </c>
       <c r="N31">
-        <v>38.75044435</v>
+        <v>38.6108045</v>
       </c>
       <c r="O31">
-        <v>11.625133305</v>
+        <v>11.58324135</v>
       </c>
       <c r="P31">
-        <v>27.125311045</v>
+        <v>27.02756315</v>
       </c>
       <c r="Q31">
-        <v>34.425311045</v>
+        <v>34.32756315</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1409379509927466</v>
+        <v>0.1419799876958435</v>
       </c>
       <c r="T31">
-        <v>0.9200566983609145</v>
+        <v>0.9301339896901688</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.56906083016787</v>
+        <v>10.21675880249561</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1102639913870904</v>
+        <v>0.1099466375693308</v>
       </c>
       <c r="C32">
-        <v>204.2287972457722</v>
+        <v>202.0899968972225</v>
       </c>
       <c r="D32">
-        <v>226.8012972457722</v>
+        <v>227.3582468972225</v>
       </c>
       <c r="E32">
-        <v>80.79749999999999</v>
+        <v>83.49324999999999</v>
       </c>
       <c r="F32">
-        <v>80.87249999999999</v>
+        <v>83.56824999999999</v>
       </c>
       <c r="G32">
         <v>58.3</v>
@@ -3905,28 +3905,28 @@
         <v>42.8</v>
       </c>
       <c r="M32">
-        <v>4.189195499999999</v>
+        <v>4.328835349999999</v>
       </c>
       <c r="N32">
-        <v>38.6108045</v>
+        <v>38.47116465</v>
       </c>
       <c r="O32">
-        <v>11.58324135</v>
+        <v>11.541349395</v>
       </c>
       <c r="P32">
-        <v>27.02756315</v>
+        <v>26.929815255</v>
       </c>
       <c r="Q32">
-        <v>34.32756315</v>
+        <v>34.22981525500001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1419799876958435</v>
+        <v>0.143052228361349</v>
       </c>
       <c r="T32">
-        <v>0.9301339896901688</v>
+        <v>0.9405033764202709</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.21675880249561</v>
+        <v>9.887185937898979</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1099466375693308</v>
+        <v>0.1100100837515711</v>
       </c>
       <c r="C33">
-        <v>202.0899968972225</v>
+        <v>199.2826814478377</v>
       </c>
       <c r="D33">
-        <v>227.3582468972225</v>
+        <v>227.2466814478377</v>
       </c>
       <c r="E33">
-        <v>83.49324999999999</v>
+        <v>86.18899999999999</v>
       </c>
       <c r="F33">
-        <v>83.56824999999999</v>
+        <v>86.264</v>
       </c>
       <c r="G33">
         <v>58.3</v>
@@ -3987,45 +3987,45 @@
         <v>42.8</v>
       </c>
       <c r="M33">
-        <v>4.328835349999999</v>
+        <v>4.615124</v>
       </c>
       <c r="N33">
-        <v>38.47116465</v>
+        <v>38.184876</v>
       </c>
       <c r="O33">
-        <v>11.541349395</v>
+        <v>11.4554628</v>
       </c>
       <c r="P33">
-        <v>26.929815255</v>
+        <v>26.7294132</v>
       </c>
       <c r="Q33">
-        <v>34.22981525500001</v>
+        <v>34.0294132</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.143052228361349</v>
+        <v>0.1441560055170164</v>
       </c>
       <c r="T33">
-        <v>0.9405033764202709</v>
+        <v>0.9511777451130232</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>9.887185937898979</v>
+        <v>9.273856997125105</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1100100837515711</v>
+        <v>0.1097046299338115</v>
       </c>
       <c r="C34">
-        <v>199.2826814478377</v>
+        <v>197.125057260617</v>
       </c>
       <c r="D34">
-        <v>227.2466814478377</v>
+        <v>227.784807260617</v>
       </c>
       <c r="E34">
-        <v>86.18899999999999</v>
+        <v>88.88475</v>
       </c>
       <c r="F34">
-        <v>86.264</v>
+        <v>88.95975</v>
       </c>
       <c r="G34">
         <v>58.3</v>
@@ -4069,28 +4069,28 @@
         <v>42.8</v>
       </c>
       <c r="M34">
-        <v>4.615124</v>
+        <v>4.759346625</v>
       </c>
       <c r="N34">
-        <v>38.184876</v>
+        <v>38.040653375</v>
       </c>
       <c r="O34">
-        <v>11.4554628</v>
+        <v>11.4121960125</v>
       </c>
       <c r="P34">
-        <v>26.7294132</v>
+        <v>26.6284573625</v>
       </c>
       <c r="Q34">
-        <v>34.0294132</v>
+        <v>33.9284573625</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1441560055170164</v>
+        <v>0.1452927312444948</v>
       </c>
       <c r="T34">
-        <v>0.9511777451130232</v>
+        <v>0.9621707516772011</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.273856997125105</v>
+        <v>8.992831027515251</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1097046299338115</v>
+        <v>0.1093991761160518</v>
       </c>
       <c r="C35">
-        <v>197.125057260617</v>
+        <v>194.969987713556</v>
       </c>
       <c r="D35">
-        <v>227.784807260617</v>
+        <v>228.325487713556</v>
       </c>
       <c r="E35">
-        <v>88.88475</v>
+        <v>91.5805</v>
       </c>
       <c r="F35">
-        <v>88.95975</v>
+        <v>91.6555</v>
       </c>
       <c r="G35">
         <v>58.3</v>
@@ -4151,28 +4151,28 @@
         <v>42.8</v>
       </c>
       <c r="M35">
-        <v>4.759346625</v>
+        <v>4.90356925</v>
       </c>
       <c r="N35">
-        <v>38.040653375</v>
+        <v>37.89643074999999</v>
       </c>
       <c r="O35">
-        <v>11.4121960125</v>
+        <v>11.368929225</v>
       </c>
       <c r="P35">
-        <v>26.6284573625</v>
+        <v>26.527501525</v>
       </c>
       <c r="Q35">
-        <v>33.9284573625</v>
+        <v>33.827501525</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1452927312444948</v>
+        <v>0.1464639032061392</v>
       </c>
       <c r="T35">
-        <v>0.9621707516772011</v>
+        <v>0.9734968796524144</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.992831027515251</v>
+        <v>8.728335997294213</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1093991761160518</v>
+        <v>0.1090937222982922</v>
       </c>
       <c r="C36">
-        <v>194.969987713556</v>
+        <v>192.8174910413701</v>
       </c>
       <c r="D36">
-        <v>228.325487713556</v>
+        <v>228.8687410413701</v>
       </c>
       <c r="E36">
-        <v>91.5805</v>
+        <v>94.27625</v>
       </c>
       <c r="F36">
-        <v>91.6555</v>
+        <v>94.35125000000001</v>
       </c>
       <c r="G36">
         <v>58.3</v>
@@ -4233,28 +4233,28 @@
         <v>42.8</v>
       </c>
       <c r="M36">
-        <v>4.90356925</v>
+        <v>5.047791875000001</v>
       </c>
       <c r="N36">
-        <v>37.89643074999999</v>
+        <v>37.752208125</v>
       </c>
       <c r="O36">
-        <v>11.368929225</v>
+        <v>11.3256624375</v>
       </c>
       <c r="P36">
-        <v>26.527501525</v>
+        <v>26.4265456875</v>
       </c>
       <c r="Q36">
-        <v>33.827501525</v>
+        <v>33.7265456875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1464639032061392</v>
+        <v>0.1476711112281419</v>
       </c>
       <c r="T36">
-        <v>0.9734968796524144</v>
+        <v>0.985171503873019</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.728335997294213</v>
+        <v>8.478954968800092</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1090937222982922</v>
+        <v>0.1087882684805326</v>
       </c>
       <c r="C37">
-        <v>192.8174910413701</v>
+        <v>190.6675856527316</v>
       </c>
       <c r="D37">
-        <v>228.8687410413701</v>
+        <v>229.4145856527316</v>
       </c>
       <c r="E37">
-        <v>94.27625</v>
+        <v>96.97200000000001</v>
       </c>
       <c r="F37">
-        <v>94.35125000000001</v>
+        <v>97.04700000000001</v>
       </c>
       <c r="G37">
         <v>58.3</v>
@@ -4315,28 +4315,28 @@
         <v>42.8</v>
       </c>
       <c r="M37">
-        <v>5.047791875000001</v>
+        <v>5.192014500000001</v>
       </c>
       <c r="N37">
-        <v>37.752208125</v>
+        <v>37.6079855</v>
       </c>
       <c r="O37">
-        <v>11.3256624375</v>
+        <v>11.28239565</v>
       </c>
       <c r="P37">
-        <v>26.4265456875</v>
+        <v>26.32558985</v>
       </c>
       <c r="Q37">
-        <v>33.7265456875</v>
+        <v>33.62558985</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1476711112281419</v>
+        <v>0.1489160445008322</v>
       </c>
       <c r="T37">
-        <v>0.985171503873019</v>
+        <v>0.9972109601005175</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.478954968800092</v>
+        <v>8.24342844188898</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1087882684805326</v>
+        <v>0.1084828146627729</v>
       </c>
       <c r="C38">
-        <v>190.6675856527316</v>
+        <v>188.5202901323491</v>
       </c>
       <c r="D38">
-        <v>229.4145856527316</v>
+        <v>229.9630401323491</v>
       </c>
       <c r="E38">
-        <v>96.97199999999999</v>
+        <v>99.66775</v>
       </c>
       <c r="F38">
-        <v>97.047</v>
+        <v>99.74275</v>
       </c>
       <c r="G38">
         <v>58.3</v>
@@ -4397,28 +4397,28 @@
         <v>42.8</v>
       </c>
       <c r="M38">
-        <v>5.1920145</v>
+        <v>5.336237125</v>
       </c>
       <c r="N38">
-        <v>37.6079855</v>
+        <v>37.463762875</v>
       </c>
       <c r="O38">
-        <v>11.28239565</v>
+        <v>11.2391288625</v>
       </c>
       <c r="P38">
-        <v>26.32558985</v>
+        <v>26.2246340125</v>
       </c>
       <c r="Q38">
-        <v>33.62558985</v>
+        <v>33.5246340125</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1489160445008322</v>
+        <v>0.150200499464719</v>
       </c>
       <c r="T38">
-        <v>0.9972109601005175</v>
+        <v>1.009632621287619</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.24342844188898</v>
+        <v>8.020633078594685</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1084828146627729</v>
+        <v>0.1081773608450133</v>
       </c>
       <c r="C39">
-        <v>188.5202901323491</v>
+        <v>186.3756232430767</v>
       </c>
       <c r="D39">
-        <v>229.9630401323491</v>
+        <v>230.5141232430767</v>
       </c>
       <c r="E39">
-        <v>99.66775</v>
+        <v>102.3635</v>
       </c>
       <c r="F39">
-        <v>99.74275</v>
+        <v>102.4385</v>
       </c>
       <c r="G39">
         <v>58.3</v>
@@ -4479,28 +4479,28 @@
         <v>42.8</v>
       </c>
       <c r="M39">
-        <v>5.336237125</v>
+        <v>5.48045975</v>
       </c>
       <c r="N39">
-        <v>37.463762875</v>
+        <v>37.31954025</v>
       </c>
       <c r="O39">
-        <v>11.2391288625</v>
+        <v>11.195862075</v>
       </c>
       <c r="P39">
-        <v>26.2246340125</v>
+        <v>26.12367817499999</v>
       </c>
       <c r="Q39">
-        <v>33.5246340125</v>
+        <v>33.423678175</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.150200499464719</v>
+        <v>0.1515263884596989</v>
       </c>
       <c r="T39">
-        <v>1.009632621287619</v>
+        <v>1.022454981222692</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.020633078594685</v>
+        <v>7.809563787052719</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1081773608450133</v>
+        <v>0.1080903070272537</v>
       </c>
       <c r="C40">
-        <v>186.3756232430767</v>
+        <v>183.8374149600944</v>
       </c>
       <c r="D40">
-        <v>230.5141232430767</v>
+        <v>230.6716649600944</v>
       </c>
       <c r="E40">
-        <v>102.3635</v>
+        <v>105.05925</v>
       </c>
       <c r="F40">
-        <v>102.4385</v>
+        <v>105.13425</v>
       </c>
       <c r="G40">
         <v>58.3</v>
@@ -4561,45 +4561,45 @@
         <v>42.8</v>
       </c>
       <c r="M40">
-        <v>5.48045975</v>
+        <v>5.708789775</v>
       </c>
       <c r="N40">
-        <v>37.31954025</v>
+        <v>37.091210225</v>
       </c>
       <c r="O40">
-        <v>11.195862075</v>
+        <v>11.1273630675</v>
       </c>
       <c r="P40">
-        <v>26.12367817499999</v>
+        <v>25.9638471575</v>
       </c>
       <c r="Q40">
-        <v>33.423678175</v>
+        <v>33.2638471575</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1515263884596989</v>
+        <v>0.152895749225006</v>
       </c>
       <c r="T40">
-        <v>1.022454981222692</v>
+        <v>1.035697746401537</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.809563787052719</v>
+        <v>7.497210737629588</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1080903070272537</v>
+        <v>0.107790453209494</v>
       </c>
       <c r="C41">
-        <v>183.8374149600944</v>
+        <v>181.6859640551764</v>
       </c>
       <c r="D41">
-        <v>230.6716649600944</v>
+        <v>231.2159640551764</v>
       </c>
       <c r="E41">
-        <v>105.05925</v>
+        <v>107.755</v>
       </c>
       <c r="F41">
-        <v>105.13425</v>
+        <v>107.83</v>
       </c>
       <c r="G41">
         <v>58.3</v>
@@ -4643,28 +4643,28 @@
         <v>42.8</v>
       </c>
       <c r="M41">
-        <v>5.708789775</v>
+        <v>5.855169</v>
       </c>
       <c r="N41">
-        <v>37.091210225</v>
+        <v>36.94483099999999</v>
       </c>
       <c r="O41">
-        <v>11.1273630675</v>
+        <v>11.0834493</v>
       </c>
       <c r="P41">
-        <v>25.9638471575</v>
+        <v>25.8613817</v>
       </c>
       <c r="Q41">
-        <v>33.2638471575</v>
+        <v>33.1613817</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.152895749225006</v>
+        <v>0.1543107553491568</v>
       </c>
       <c r="T41">
-        <v>1.035697746401537</v>
+        <v>1.049381937086344</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.497210737629588</v>
+        <v>7.309780469188847</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.107790453209494</v>
+        <v>0.1074905993917344</v>
       </c>
       <c r="C42">
-        <v>181.6859640551764</v>
+        <v>179.5370879114459</v>
       </c>
       <c r="D42">
-        <v>231.2159640551764</v>
+        <v>231.7628379114459</v>
       </c>
       <c r="E42">
-        <v>107.755</v>
+        <v>110.45075</v>
       </c>
       <c r="F42">
-        <v>107.83</v>
+        <v>110.52575</v>
       </c>
       <c r="G42">
         <v>58.3</v>
@@ -4725,28 +4725,28 @@
         <v>42.8</v>
       </c>
       <c r="M42">
-        <v>5.855169</v>
+        <v>6.001548225000001</v>
       </c>
       <c r="N42">
-        <v>36.94483099999999</v>
+        <v>36.798451775</v>
       </c>
       <c r="O42">
-        <v>11.0834493</v>
+        <v>11.0395355325</v>
       </c>
       <c r="P42">
-        <v>25.8613817</v>
+        <v>25.7589162425</v>
       </c>
       <c r="Q42">
-        <v>33.1613817</v>
+        <v>33.0589162425</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1543107553491568</v>
+        <v>0.1557737277826007</v>
       </c>
       <c r="T42">
-        <v>1.049381937086344</v>
+        <v>1.063529998641823</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.309780469188847</v>
+        <v>7.131493140672046</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1074905993917344</v>
+        <v>0.1071907455739748</v>
       </c>
       <c r="C43">
-        <v>179.5370879114459</v>
+        <v>177.3908048417542</v>
       </c>
       <c r="D43">
-        <v>231.7628379114459</v>
+        <v>232.3123048417542</v>
       </c>
       <c r="E43">
-        <v>110.45075</v>
+        <v>113.1465</v>
       </c>
       <c r="F43">
-        <v>110.52575</v>
+        <v>113.2215</v>
       </c>
       <c r="G43">
         <v>58.3</v>
@@ -4807,28 +4807,28 @@
         <v>42.8</v>
       </c>
       <c r="M43">
-        <v>6.001548225000001</v>
+        <v>6.14792745</v>
       </c>
       <c r="N43">
-        <v>36.798451775</v>
+        <v>36.65207255</v>
       </c>
       <c r="O43">
-        <v>11.0395355325</v>
+        <v>10.995621765</v>
       </c>
       <c r="P43">
-        <v>25.7589162425</v>
+        <v>25.656450785</v>
       </c>
       <c r="Q43">
-        <v>33.0589162425</v>
+        <v>32.956450785</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1557737277826007</v>
+        <v>0.1572871475413358</v>
       </c>
       <c r="T43">
-        <v>1.063529998641823</v>
+        <v>1.078165924388869</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.131493140672046</v>
+        <v>6.96169568494176</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1071907455739748</v>
+        <v>0.1068908917562151</v>
       </c>
       <c r="C44">
-        <v>177.3908048417542</v>
+        <v>175.2471333330307</v>
       </c>
       <c r="D44">
-        <v>232.3123048417542</v>
+        <v>232.8643833330307</v>
       </c>
       <c r="E44">
-        <v>113.1465</v>
+        <v>115.84225</v>
       </c>
       <c r="F44">
-        <v>113.2215</v>
+        <v>115.91725</v>
       </c>
       <c r="G44">
         <v>58.3</v>
@@ -4889,28 +4889,28 @@
         <v>42.8</v>
       </c>
       <c r="M44">
-        <v>6.14792745</v>
+        <v>6.294306675</v>
       </c>
       <c r="N44">
-        <v>36.65207255</v>
+        <v>36.505693325</v>
       </c>
       <c r="O44">
-        <v>10.995621765</v>
+        <v>10.9517079975</v>
       </c>
       <c r="P44">
-        <v>25.656450785</v>
+        <v>25.5539853275</v>
       </c>
       <c r="Q44">
-        <v>32.956450785</v>
+        <v>32.8539853275</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1572871475413358</v>
+        <v>0.1588536697477458</v>
       </c>
       <c r="T44">
-        <v>1.078165924388869</v>
+        <v>1.093315391390198</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.96169568494176</v>
+        <v>6.799795785291952</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1068908917562151</v>
+        <v>0.1065910379384555</v>
       </c>
       <c r="C45">
-        <v>175.2471333330307</v>
+        <v>173.1060920483568</v>
       </c>
       <c r="D45">
-        <v>232.8643833330307</v>
+        <v>233.4190920483568</v>
       </c>
       <c r="E45">
-        <v>115.84225</v>
+        <v>118.538</v>
       </c>
       <c r="F45">
-        <v>115.91725</v>
+        <v>118.613</v>
       </c>
       <c r="G45">
         <v>58.3</v>
@@ -4971,28 +4971,28 @@
         <v>42.8</v>
       </c>
       <c r="M45">
-        <v>6.294306675</v>
+        <v>6.4406859</v>
       </c>
       <c r="N45">
-        <v>36.505693325</v>
+        <v>36.3593141</v>
       </c>
       <c r="O45">
-        <v>10.9517079975</v>
+        <v>10.90779423</v>
       </c>
       <c r="P45">
-        <v>25.5539853275</v>
+        <v>25.45151987</v>
       </c>
       <c r="Q45">
-        <v>32.8539853275</v>
+        <v>32.75151987</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1588536697477458</v>
+        <v>0.1604761391758134</v>
       </c>
       <c r="T45">
-        <v>1.093315391390198</v>
+        <v>1.109005910784432</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.799795785291952</v>
+        <v>6.645254971989861</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1065910379384555</v>
+        <v>0.1062911841206959</v>
       </c>
       <c r="C46">
-        <v>173.1060920483568</v>
+        <v>170.9676998290682</v>
       </c>
       <c r="D46">
-        <v>233.4190920483568</v>
+        <v>233.9764498290682</v>
       </c>
       <c r="E46">
-        <v>118.538</v>
+        <v>121.23375</v>
       </c>
       <c r="F46">
-        <v>118.613</v>
+        <v>121.30875</v>
       </c>
       <c r="G46">
         <v>58.3</v>
@@ -5053,28 +5053,28 @@
         <v>42.8</v>
       </c>
       <c r="M46">
-        <v>6.4406859</v>
+        <v>6.587065125000001</v>
       </c>
       <c r="N46">
-        <v>36.3593141</v>
+        <v>36.21293487499999</v>
       </c>
       <c r="O46">
-        <v>10.90779423</v>
+        <v>10.8638804625</v>
       </c>
       <c r="P46">
-        <v>25.45151987</v>
+        <v>25.3490544125</v>
       </c>
       <c r="Q46">
-        <v>32.75151987</v>
+        <v>32.6490544125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1604761391758134</v>
+        <v>0.1621576074921743</v>
       </c>
       <c r="T46">
-        <v>1.109005910784432</v>
+        <v>1.125266994520274</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.645254971989861</v>
+        <v>6.497582639278975</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1062911841206959</v>
+        <v>0.1059913303029362</v>
       </c>
       <c r="C47">
-        <v>170.9676998290682</v>
+        <v>168.8319756968889</v>
       </c>
       <c r="D47">
-        <v>233.9764498290682</v>
+        <v>234.5364756968889</v>
       </c>
       <c r="E47">
-        <v>121.23375</v>
+        <v>123.9295</v>
       </c>
       <c r="F47">
-        <v>121.30875</v>
+        <v>124.0045</v>
       </c>
       <c r="G47">
         <v>58.3</v>
@@ -5135,28 +5135,28 @@
         <v>42.8</v>
       </c>
       <c r="M47">
-        <v>6.587065125000001</v>
+        <v>6.73344435</v>
       </c>
       <c r="N47">
-        <v>36.21293487499999</v>
+        <v>36.06655565</v>
       </c>
       <c r="O47">
-        <v>10.8638804625</v>
+        <v>10.819966695</v>
       </c>
       <c r="P47">
-        <v>25.3490544125</v>
+        <v>25.246588955</v>
       </c>
       <c r="Q47">
-        <v>32.6490544125</v>
+        <v>32.546588955</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1621576074921743</v>
+        <v>0.1639013524128448</v>
       </c>
       <c r="T47">
-        <v>1.125266994520274</v>
+        <v>1.142130340616703</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.497582639278975</v>
+        <v>6.356330842772911</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1059913303029362</v>
+        <v>0.1056914764851766</v>
       </c>
       <c r="C48">
-        <v>168.8319756968889</v>
+        <v>166.6989388560947</v>
       </c>
       <c r="D48">
-        <v>234.5364756968889</v>
+        <v>235.0991888560947</v>
       </c>
       <c r="E48">
-        <v>123.9295</v>
+        <v>126.62525</v>
       </c>
       <c r="F48">
-        <v>124.0045</v>
+        <v>126.70025</v>
       </c>
       <c r="G48">
         <v>58.3</v>
@@ -5217,28 +5217,28 @@
         <v>42.8</v>
       </c>
       <c r="M48">
-        <v>6.73344435</v>
+        <v>6.879823575</v>
       </c>
       <c r="N48">
-        <v>36.06655565</v>
+        <v>35.92017642499999</v>
       </c>
       <c r="O48">
-        <v>10.819966695</v>
+        <v>10.7760529275</v>
       </c>
       <c r="P48">
-        <v>25.246588955</v>
+        <v>25.1441234975</v>
       </c>
       <c r="Q48">
-        <v>32.546588955</v>
+        <v>32.4441234975</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1639013524128448</v>
+        <v>0.165710899028635</v>
       </c>
       <c r="T48">
-        <v>1.142130340616703</v>
+        <v>1.159630039396016</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.356330842772911</v>
+        <v>6.221089761011785</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1056914764851766</v>
+        <v>0.1057276226674169</v>
       </c>
       <c r="C49">
-        <v>166.6989388560947</v>
+        <v>163.9352129399371</v>
       </c>
       <c r="D49">
-        <v>235.0991888560947</v>
+        <v>235.0312129399371</v>
       </c>
       <c r="E49">
-        <v>126.62525</v>
+        <v>129.321</v>
       </c>
       <c r="F49">
-        <v>126.70025</v>
+        <v>129.396</v>
       </c>
       <c r="G49">
         <v>58.3</v>
@@ -5299,45 +5299,45 @@
         <v>42.8</v>
       </c>
       <c r="M49">
-        <v>6.879823575</v>
+        <v>7.155598800000001</v>
       </c>
       <c r="N49">
-        <v>35.92017642499999</v>
+        <v>35.6444012</v>
       </c>
       <c r="O49">
-        <v>10.7760529275</v>
+        <v>10.69332036</v>
       </c>
       <c r="P49">
-        <v>25.1441234975</v>
+        <v>24.95108084</v>
       </c>
       <c r="Q49">
-        <v>32.4441234975</v>
+        <v>32.25108084</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.165710899028635</v>
+        <v>0.1675900435911864</v>
       </c>
       <c r="T49">
-        <v>1.159630039396016</v>
+        <v>1.177802803512995</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.221089761011785</v>
+        <v>5.98133031158762</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1057276226674169</v>
+        <v>0.1054347688496573</v>
       </c>
       <c r="C50">
-        <v>163.9352129399371</v>
+        <v>161.7913325701663</v>
       </c>
       <c r="D50">
-        <v>235.0312129399371</v>
+        <v>235.5830825701663</v>
       </c>
       <c r="E50">
-        <v>129.321</v>
+        <v>132.01675</v>
       </c>
       <c r="F50">
-        <v>129.396</v>
+        <v>132.09175</v>
       </c>
       <c r="G50">
         <v>58.3</v>
@@ -5381,28 +5381,28 @@
         <v>42.8</v>
       </c>
       <c r="M50">
-        <v>7.1555988</v>
+        <v>7.304673774999999</v>
       </c>
       <c r="N50">
-        <v>35.6444012</v>
+        <v>35.495326225</v>
       </c>
       <c r="O50">
-        <v>10.69332036</v>
+        <v>10.6485978675</v>
       </c>
       <c r="P50">
-        <v>24.95108084</v>
+        <v>24.8467283575</v>
       </c>
       <c r="Q50">
-        <v>32.25108084</v>
+        <v>32.1467283575</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1675900435911864</v>
+        <v>0.1695428800973672</v>
       </c>
       <c r="T50">
-        <v>1.177802803512995</v>
+        <v>1.196688225046326</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.98133031158762</v>
+        <v>5.859262346045016</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1054347688496573</v>
+        <v>0.1051419150318977</v>
       </c>
       <c r="C51">
-        <v>161.7913325701663</v>
+        <v>159.6500499566367</v>
       </c>
       <c r="D51">
-        <v>235.5830825701663</v>
+        <v>236.1375499566367</v>
       </c>
       <c r="E51">
-        <v>132.01675</v>
+        <v>134.7125</v>
       </c>
       <c r="F51">
-        <v>132.09175</v>
+        <v>134.7875</v>
       </c>
       <c r="G51">
         <v>58.3</v>
@@ -5463,28 +5463,28 @@
         <v>42.8</v>
       </c>
       <c r="M51">
-        <v>7.304673774999999</v>
+        <v>7.45374875</v>
       </c>
       <c r="N51">
-        <v>35.495326225</v>
+        <v>35.34625124999999</v>
       </c>
       <c r="O51">
-        <v>10.6485978675</v>
+        <v>10.603875375</v>
       </c>
       <c r="P51">
-        <v>24.8467283575</v>
+        <v>24.742375875</v>
       </c>
       <c r="Q51">
-        <v>32.1467283575</v>
+        <v>32.042375875</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1695428800973672</v>
+        <v>0.1715738300637953</v>
       </c>
       <c r="T51">
-        <v>1.196688225046326</v>
+        <v>1.21632906344099</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.859262346045016</v>
+        <v>5.742077099124114</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1051419150318977</v>
+        <v>0.104849061214138</v>
       </c>
       <c r="C52">
-        <v>159.6500499566367</v>
+        <v>157.511383484826</v>
       </c>
       <c r="D52">
-        <v>236.1375499566367</v>
+        <v>236.694633484826</v>
       </c>
       <c r="E52">
-        <v>134.7125</v>
+        <v>137.40825</v>
       </c>
       <c r="F52">
-        <v>134.7875</v>
+        <v>137.48325</v>
       </c>
       <c r="G52">
         <v>58.3</v>
@@ -5545,28 +5545,28 @@
         <v>42.8</v>
       </c>
       <c r="M52">
-        <v>7.45374875</v>
+        <v>7.602823725</v>
       </c>
       <c r="N52">
-        <v>35.34625124999999</v>
+        <v>35.197176275</v>
       </c>
       <c r="O52">
-        <v>10.603875375</v>
+        <v>10.5591528825</v>
       </c>
       <c r="P52">
-        <v>24.742375875</v>
+        <v>24.6380233925</v>
       </c>
       <c r="Q52">
-        <v>32.042375875</v>
+        <v>31.9380233925</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1715738300637953</v>
+        <v>0.1736876759472205</v>
       </c>
       <c r="T52">
-        <v>1.21632906344099</v>
+        <v>1.236771568708906</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.742077099124114</v>
+        <v>5.629487352082466</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.104849061214138</v>
+        <v>0.1045562073963784</v>
       </c>
       <c r="C53">
-        <v>157.511383484826</v>
+        <v>155.3753517141184</v>
       </c>
       <c r="D53">
-        <v>236.694633484826</v>
+        <v>237.2543517141184</v>
       </c>
       <c r="E53">
-        <v>137.40825</v>
+        <v>140.104</v>
       </c>
       <c r="F53">
-        <v>137.48325</v>
+        <v>140.179</v>
       </c>
       <c r="G53">
         <v>58.3</v>
@@ -5627,28 +5627,28 @@
         <v>42.8</v>
       </c>
       <c r="M53">
-        <v>7.602823725</v>
+        <v>7.751898700000001</v>
       </c>
       <c r="N53">
-        <v>35.197176275</v>
+        <v>35.0481013</v>
       </c>
       <c r="O53">
-        <v>10.5591528825</v>
+        <v>10.51443039</v>
       </c>
       <c r="P53">
-        <v>24.6380233925</v>
+        <v>24.53367091</v>
       </c>
       <c r="Q53">
-        <v>31.9380233925</v>
+        <v>31.83367091</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1736876759472205</v>
+        <v>0.175889598742455</v>
       </c>
       <c r="T53">
-        <v>1.236771568708906</v>
+        <v>1.258065845029651</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.629487352082466</v>
+        <v>5.521227979927033</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1045562073963784</v>
+        <v>0.1042633535786187</v>
       </c>
       <c r="C54">
-        <v>155.3753517141184</v>
+        <v>153.2419733798656</v>
       </c>
       <c r="D54">
-        <v>237.2543517141184</v>
+        <v>237.8167233798656</v>
       </c>
       <c r="E54">
-        <v>140.104</v>
+        <v>142.79975</v>
       </c>
       <c r="F54">
-        <v>140.179</v>
+        <v>142.87475</v>
       </c>
       <c r="G54">
         <v>58.3</v>
@@ -5709,28 +5709,28 @@
         <v>42.8</v>
       </c>
       <c r="M54">
-        <v>7.751898700000001</v>
+        <v>7.900973675</v>
       </c>
       <c r="N54">
-        <v>35.0481013</v>
+        <v>34.89902632499999</v>
       </c>
       <c r="O54">
-        <v>10.51443039</v>
+        <v>10.4697078975</v>
       </c>
       <c r="P54">
-        <v>24.53367091</v>
+        <v>24.4293184275</v>
       </c>
       <c r="Q54">
-        <v>31.83367091</v>
+        <v>31.7293184275</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.175889598742455</v>
+        <v>0.1781852203800399</v>
       </c>
       <c r="T54">
-        <v>1.258065845029651</v>
+        <v>1.280266260768301</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.521227979927033</v>
+        <v>5.417053867098221</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1042633535786187</v>
+        <v>0.1039704997608591</v>
       </c>
       <c r="C55">
-        <v>153.2419733798656</v>
+        <v>151.1112673954777</v>
       </c>
       <c r="D55">
-        <v>237.8167233798656</v>
+        <v>238.3817673954777</v>
       </c>
       <c r="E55">
-        <v>142.79975</v>
+        <v>145.4955</v>
       </c>
       <c r="F55">
-        <v>142.87475</v>
+        <v>145.5705</v>
       </c>
       <c r="G55">
         <v>58.3</v>
@@ -5791,28 +5791,28 @@
         <v>42.8</v>
       </c>
       <c r="M55">
-        <v>7.900973675</v>
+        <v>8.050048650000001</v>
       </c>
       <c r="N55">
-        <v>34.89902632499999</v>
+        <v>34.74995135</v>
       </c>
       <c r="O55">
-        <v>10.4697078975</v>
+        <v>10.424985405</v>
       </c>
       <c r="P55">
-        <v>24.4293184275</v>
+        <v>24.324965945</v>
       </c>
       <c r="Q55">
-        <v>31.7293184275</v>
+        <v>31.624965945</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1781852203800399</v>
+        <v>0.1805806516540415</v>
       </c>
       <c r="T55">
-        <v>1.280266260768301</v>
+        <v>1.303431911973848</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.417053867098221</v>
+        <v>5.31673805474455</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1039704997608591</v>
+        <v>0.1036776459430995</v>
       </c>
       <c r="C56">
-        <v>151.1112673954777</v>
+        <v>148.9832528545427</v>
       </c>
       <c r="D56">
-        <v>238.3817673954777</v>
+        <v>238.9495028545427</v>
       </c>
       <c r="E56">
-        <v>145.4955</v>
+        <v>148.19125</v>
       </c>
       <c r="F56">
-        <v>145.5705</v>
+        <v>148.26625</v>
       </c>
       <c r="G56">
         <v>58.3</v>
@@ -5873,28 +5873,28 @@
         <v>42.8</v>
       </c>
       <c r="M56">
-        <v>8.050048650000001</v>
+        <v>8.199123625</v>
       </c>
       <c r="N56">
-        <v>34.74995135</v>
+        <v>34.600876375</v>
       </c>
       <c r="O56">
-        <v>10.424985405</v>
+        <v>10.3802629125</v>
       </c>
       <c r="P56">
-        <v>24.324965945</v>
+        <v>24.2206134625</v>
       </c>
       <c r="Q56">
-        <v>31.624965945</v>
+        <v>31.5206134625</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1805806516540415</v>
+        <v>0.183082546540221</v>
       </c>
       <c r="T56">
-        <v>1.303431911973848</v>
+        <v>1.32762714767742</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.31673805474455</v>
+        <v>5.220070090112832</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1036776459430995</v>
+        <v>0.1033847921253398</v>
       </c>
       <c r="C57">
-        <v>148.9832528545427</v>
+        <v>146.8579490329783</v>
       </c>
       <c r="D57">
-        <v>238.9495028545427</v>
+        <v>239.5199490329784</v>
       </c>
       <c r="E57">
-        <v>148.19125</v>
+        <v>150.887</v>
       </c>
       <c r="F57">
-        <v>148.26625</v>
+        <v>150.962</v>
       </c>
       <c r="G57">
         <v>58.3</v>
@@ -5955,28 +5955,28 @@
         <v>42.8</v>
       </c>
       <c r="M57">
-        <v>8.199123625</v>
+        <v>8.348198600000002</v>
       </c>
       <c r="N57">
-        <v>34.600876375</v>
+        <v>34.45180139999999</v>
       </c>
       <c r="O57">
-        <v>10.3802629125</v>
+        <v>10.33554042</v>
       </c>
       <c r="P57">
-        <v>24.2206134625</v>
+        <v>24.11626098</v>
       </c>
       <c r="Q57">
-        <v>31.5206134625</v>
+        <v>31.41626098</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.183082546540221</v>
+        <v>0.1856981639212269</v>
       </c>
       <c r="T57">
-        <v>1.32762714767742</v>
+        <v>1.352922166822064</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.220070090112832</v>
+        <v>5.126854552789387</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1033847921253398</v>
+        <v>0.1030919383075802</v>
       </c>
       <c r="C58">
-        <v>146.8579490329783</v>
+        <v>144.7353753912127</v>
       </c>
       <c r="D58">
-        <v>239.5199490329784</v>
+        <v>240.0931253912127</v>
       </c>
       <c r="E58">
-        <v>150.887</v>
+        <v>153.58275</v>
       </c>
       <c r="F58">
-        <v>150.962</v>
+        <v>153.65775</v>
       </c>
       <c r="G58">
         <v>58.3</v>
@@ -6037,28 +6037,28 @@
         <v>42.8</v>
       </c>
       <c r="M58">
-        <v>8.348198600000002</v>
+        <v>8.497273575000001</v>
       </c>
       <c r="N58">
-        <v>34.45180139999999</v>
+        <v>34.302726425</v>
       </c>
       <c r="O58">
-        <v>10.33554042</v>
+        <v>10.2908179275</v>
       </c>
       <c r="P58">
-        <v>24.11626098</v>
+        <v>24.0119084975</v>
       </c>
       <c r="Q58">
-        <v>31.41626098</v>
+        <v>31.3119084975</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1856981639212269</v>
+        <v>0.1884354379246051</v>
       </c>
       <c r="T58">
-        <v>1.352922166822064</v>
+        <v>1.379393698485063</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.126854552789387</v>
+        <v>5.036909736073784</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1030919383075802</v>
+        <v>0.1027990844898205</v>
       </c>
       <c r="C59">
-        <v>144.7353753912127</v>
+        <v>142.6155515763978</v>
       </c>
       <c r="D59">
-        <v>240.0931253912127</v>
+        <v>240.6690515763978</v>
       </c>
       <c r="E59">
-        <v>153.58275</v>
+        <v>156.2785</v>
       </c>
       <c r="F59">
-        <v>153.65775</v>
+        <v>156.3535</v>
       </c>
       <c r="G59">
         <v>58.3</v>
@@ -6119,28 +6119,28 @@
         <v>42.8</v>
       </c>
       <c r="M59">
-        <v>8.497273575000001</v>
+        <v>8.646348550000003</v>
       </c>
       <c r="N59">
-        <v>34.302726425</v>
+        <v>34.15365145</v>
       </c>
       <c r="O59">
-        <v>10.2908179275</v>
+        <v>10.246095435</v>
       </c>
       <c r="P59">
-        <v>24.0119084975</v>
+        <v>23.907556015</v>
       </c>
       <c r="Q59">
-        <v>31.3119084975</v>
+        <v>31.207556015</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1884354379246051</v>
+        <v>0.1913030583090966</v>
       </c>
       <c r="T59">
-        <v>1.379393698485063</v>
+        <v>1.407125779274871</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.036909736073784</v>
+        <v>4.950066464762167</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1027990844898205</v>
+        <v>0.1025062306720609</v>
       </c>
       <c r="C60">
-        <v>142.6155515763979</v>
+        <v>140.4984974246542</v>
       </c>
       <c r="D60">
-        <v>240.6690515763979</v>
+        <v>241.2477474246542</v>
       </c>
       <c r="E60">
-        <v>156.2785</v>
+        <v>158.97425</v>
       </c>
       <c r="F60">
-        <v>156.3535</v>
+        <v>159.04925</v>
       </c>
       <c r="G60">
         <v>58.3</v>
@@ -6201,28 +6201,28 @@
         <v>42.8</v>
       </c>
       <c r="M60">
-        <v>8.646348550000001</v>
+        <v>8.795423524999999</v>
       </c>
       <c r="N60">
-        <v>34.15365145</v>
+        <v>34.004576475</v>
       </c>
       <c r="O60">
-        <v>10.246095435</v>
+        <v>10.2013729425</v>
       </c>
       <c r="P60">
-        <v>23.907556015</v>
+        <v>23.8032035325</v>
       </c>
       <c r="Q60">
-        <v>31.207556015</v>
+        <v>31.1032035325</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1913030583090965</v>
+        <v>0.1943105626147827</v>
       </c>
       <c r="T60">
-        <v>1.40712577927487</v>
+        <v>1.43621064449345</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.950066464762168</v>
+        <v>4.866167033156031</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1025062306720609</v>
+        <v>0.1022133768543013</v>
       </c>
       <c r="C61">
-        <v>140.4984974246542</v>
+        <v>138.3842329633482</v>
       </c>
       <c r="D61">
-        <v>241.2477474246542</v>
+        <v>241.8292329633482</v>
       </c>
       <c r="E61">
-        <v>158.97425</v>
+        <v>161.67</v>
       </c>
       <c r="F61">
-        <v>159.04925</v>
+        <v>161.745</v>
       </c>
       <c r="G61">
         <v>58.3</v>
@@ -6283,28 +6283,28 @@
         <v>42.8</v>
       </c>
       <c r="M61">
-        <v>8.795423524999999</v>
+        <v>8.944498499999998</v>
       </c>
       <c r="N61">
-        <v>34.004576475</v>
+        <v>33.8555015</v>
       </c>
       <c r="O61">
-        <v>10.2013729425</v>
+        <v>10.15665045</v>
       </c>
       <c r="P61">
-        <v>23.8032035325</v>
+        <v>23.69885105</v>
       </c>
       <c r="Q61">
-        <v>31.1032035325</v>
+        <v>30.99885105000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1943105626147827</v>
+        <v>0.1974684421357532</v>
       </c>
       <c r="T61">
-        <v>1.43621064449345</v>
+        <v>1.466749752972958</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.866167033156031</v>
+        <v>4.785064249270097</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1022133768543013</v>
+        <v>0.1019205230365416</v>
       </c>
       <c r="C62">
-        <v>138.3842329633482</v>
+        <v>136.272778413403</v>
       </c>
       <c r="D62">
-        <v>241.8292329633482</v>
+        <v>242.413528413403</v>
       </c>
       <c r="E62">
-        <v>161.67</v>
+        <v>164.36575</v>
       </c>
       <c r="F62">
-        <v>161.745</v>
+        <v>164.44075</v>
       </c>
       <c r="G62">
         <v>58.3</v>
@@ -6365,28 +6365,28 @@
         <v>42.8</v>
       </c>
       <c r="M62">
-        <v>8.944498499999998</v>
+        <v>9.093573474999999</v>
       </c>
       <c r="N62">
-        <v>33.8555015</v>
+        <v>33.706426525</v>
       </c>
       <c r="O62">
-        <v>10.15665045</v>
+        <v>10.1119279575</v>
       </c>
       <c r="P62">
-        <v>23.69885105</v>
+        <v>23.5944985675</v>
       </c>
       <c r="Q62">
-        <v>30.99885105000001</v>
+        <v>30.8944985675</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1974684421357532</v>
+        <v>0.2007882641962606</v>
       </c>
       <c r="T62">
-        <v>1.466749752972958</v>
+        <v>1.498854969579621</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.785064249270097</v>
+        <v>4.706620573052554</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1019205230365416</v>
+        <v>0.101627669218782</v>
       </c>
       <c r="C63">
-        <v>136.272778413403</v>
+        <v>134.1641541916419</v>
       </c>
       <c r="D63">
-        <v>242.413528413403</v>
+        <v>243.0006541916419</v>
       </c>
       <c r="E63">
-        <v>164.36575</v>
+        <v>167.0615</v>
       </c>
       <c r="F63">
-        <v>164.44075</v>
+        <v>167.1365</v>
       </c>
       <c r="G63">
         <v>58.3</v>
@@ -6447,28 +6447,28 @@
         <v>42.8</v>
       </c>
       <c r="M63">
-        <v>9.093573474999999</v>
+        <v>9.242648449999999</v>
       </c>
       <c r="N63">
-        <v>33.706426525</v>
+        <v>33.55735155</v>
       </c>
       <c r="O63">
-        <v>10.1119279575</v>
+        <v>10.067205465</v>
       </c>
       <c r="P63">
-        <v>23.5944985675</v>
+        <v>23.490146085</v>
       </c>
       <c r="Q63">
-        <v>30.8944985675</v>
+        <v>30.790146085</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2007882641962606</v>
+        <v>0.2042828137336368</v>
       </c>
       <c r="T63">
-        <v>1.498854969579621</v>
+        <v>1.532649934428739</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.706620573052554</v>
+        <v>4.630707338003319</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.101627669218782</v>
+        <v>0.1013348154010224</v>
       </c>
       <c r="C64">
-        <v>134.1641541916419</v>
+        <v>132.0583809131667</v>
       </c>
       <c r="D64">
-        <v>243.0006541916419</v>
+        <v>243.5906309131666</v>
       </c>
       <c r="E64">
-        <v>167.0615</v>
+        <v>169.75725</v>
       </c>
       <c r="F64">
-        <v>167.1365</v>
+        <v>169.83225</v>
       </c>
       <c r="G64">
         <v>58.3</v>
@@ -6529,28 +6529,28 @@
         <v>42.8</v>
       </c>
       <c r="M64">
-        <v>9.242648449999999</v>
+        <v>9.391723425</v>
       </c>
       <c r="N64">
-        <v>33.55735155</v>
+        <v>33.408276575</v>
       </c>
       <c r="O64">
-        <v>10.067205465</v>
+        <v>10.0224829725</v>
       </c>
       <c r="P64">
-        <v>23.490146085</v>
+        <v>23.38579360249999</v>
       </c>
       <c r="Q64">
-        <v>30.790146085</v>
+        <v>30.6857936025</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2042828137336368</v>
+        <v>0.207966257840601</v>
       </c>
       <c r="T64">
-        <v>1.532649934428739</v>
+        <v>1.568271654134567</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.630707338003319</v>
+        <v>4.5572040469239</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1013348154010224</v>
+        <v>0.1021619615832627</v>
       </c>
       <c r="C65">
-        <v>132.0583809131667</v>
+        <v>127.7036116395315</v>
       </c>
       <c r="D65">
-        <v>243.5906309131666</v>
+        <v>241.9316116395316</v>
       </c>
       <c r="E65">
-        <v>169.75725</v>
+        <v>172.453</v>
       </c>
       <c r="F65">
-        <v>169.83225</v>
+        <v>172.528</v>
       </c>
       <c r="G65">
         <v>58.3</v>
@@ -6611,45 +6611,45 @@
         <v>42.8</v>
       </c>
       <c r="M65">
-        <v>9.391723425</v>
+        <v>9.972118399999999</v>
       </c>
       <c r="N65">
-        <v>33.408276575</v>
+        <v>32.8278816</v>
       </c>
       <c r="O65">
-        <v>10.0224829725</v>
+        <v>9.848364479999999</v>
       </c>
       <c r="P65">
-        <v>23.38579360249999</v>
+        <v>22.97951712</v>
       </c>
       <c r="Q65">
-        <v>30.6857936025</v>
+        <v>30.27951712</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.207966257840601</v>
+        <v>0.2118543377312853</v>
       </c>
       <c r="T65">
-        <v>1.568271654134567</v>
+        <v>1.605872358268497</v>
       </c>
       <c r="U65">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>4.5572040469239</v>
+        <v>4.29196668984596</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1021619615832627</v>
+        <v>0.1018866077655031</v>
       </c>
       <c r="C66">
-        <v>127.7036116395315</v>
+        <v>125.5576278896273</v>
       </c>
       <c r="D66">
-        <v>241.9316116395316</v>
+        <v>242.4813778896273</v>
       </c>
       <c r="E66">
-        <v>172.453</v>
+        <v>175.14875</v>
       </c>
       <c r="F66">
-        <v>172.528</v>
+        <v>175.22375</v>
       </c>
       <c r="G66">
         <v>58.3</v>
@@ -6693,28 +6693,28 @@
         <v>42.8</v>
       </c>
       <c r="M66">
-        <v>9.972118399999999</v>
+        <v>10.12793275</v>
       </c>
       <c r="N66">
-        <v>32.8278816</v>
+        <v>32.67206725</v>
       </c>
       <c r="O66">
-        <v>9.848364479999999</v>
+        <v>9.801620174999998</v>
       </c>
       <c r="P66">
-        <v>22.97951712</v>
+        <v>22.870447075</v>
       </c>
       <c r="Q66">
-        <v>30.27951712</v>
+        <v>30.17044707500001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2118543377312853</v>
+        <v>0.2159645936157231</v>
       </c>
       <c r="T66">
-        <v>1.605872358268497</v>
+        <v>1.645621674067222</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.29196668984596</v>
+        <v>4.2259364330791</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1018866077655031</v>
+        <v>0.1016112539477434</v>
       </c>
       <c r="C67">
-        <v>125.5576278896273</v>
+        <v>123.4141484119831</v>
       </c>
       <c r="D67">
-        <v>242.4813778896273</v>
+        <v>243.0336484119831</v>
       </c>
       <c r="E67">
-        <v>175.14875</v>
+        <v>177.8445</v>
       </c>
       <c r="F67">
-        <v>175.22375</v>
+        <v>177.9195</v>
       </c>
       <c r="G67">
         <v>58.3</v>
@@ -6775,28 +6775,28 @@
         <v>42.8</v>
       </c>
       <c r="M67">
-        <v>10.12793275</v>
+        <v>10.2837471</v>
       </c>
       <c r="N67">
-        <v>32.67206725</v>
+        <v>32.5162529</v>
       </c>
       <c r="O67">
-        <v>9.801620174999998</v>
+        <v>9.754875869999999</v>
       </c>
       <c r="P67">
-        <v>22.870447075</v>
+        <v>22.76137703</v>
       </c>
       <c r="Q67">
-        <v>30.17044707500001</v>
+        <v>30.06137703</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2159645936157231</v>
+        <v>0.2203166292580689</v>
       </c>
       <c r="T67">
-        <v>1.645621674067222</v>
+        <v>1.687709184912931</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.2259364330791</v>
+        <v>4.161907093183961</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1016112539477434</v>
+        <v>0.1013359001299838</v>
       </c>
       <c r="C68">
-        <v>123.4141484119831</v>
+        <v>121.2731903566943</v>
       </c>
       <c r="D68">
-        <v>243.0336484119831</v>
+        <v>243.5884403566943</v>
       </c>
       <c r="E68">
-        <v>177.8445</v>
+        <v>180.54025</v>
       </c>
       <c r="F68">
-        <v>177.9195</v>
+        <v>180.61525</v>
       </c>
       <c r="G68">
         <v>58.3</v>
@@ -6857,28 +6857,28 @@
         <v>42.8</v>
       </c>
       <c r="M68">
-        <v>10.2837471</v>
+        <v>10.43956145</v>
       </c>
       <c r="N68">
-        <v>32.5162529</v>
+        <v>32.36043855</v>
       </c>
       <c r="O68">
-        <v>9.754875869999999</v>
+        <v>9.708131564999999</v>
       </c>
       <c r="P68">
-        <v>22.76137703</v>
+        <v>22.652306985</v>
       </c>
       <c r="Q68">
-        <v>30.06137703</v>
+        <v>29.952306985</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2203166292580689</v>
+        <v>0.2249324246363145</v>
       </c>
       <c r="T68">
-        <v>1.687709184912931</v>
+        <v>1.732347453991713</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.161907093183961</v>
+        <v>4.099789076867783</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1013359001299838</v>
+        <v>0.1010605463122242</v>
       </c>
       <c r="C69">
-        <v>121.2731903566943</v>
+        <v>119.1347710308138</v>
       </c>
       <c r="D69">
-        <v>243.5884403566943</v>
+        <v>244.1457710308138</v>
       </c>
       <c r="E69">
-        <v>180.54025</v>
+        <v>183.236</v>
       </c>
       <c r="F69">
-        <v>180.61525</v>
+        <v>183.311</v>
       </c>
       <c r="G69">
         <v>58.3</v>
@@ -6939,28 +6939,28 @@
         <v>42.8</v>
       </c>
       <c r="M69">
-        <v>10.43956145</v>
+        <v>10.5953758</v>
       </c>
       <c r="N69">
-        <v>32.36043855</v>
+        <v>32.2046242</v>
       </c>
       <c r="O69">
-        <v>9.708131564999999</v>
+        <v>9.66138726</v>
       </c>
       <c r="P69">
-        <v>22.652306985</v>
+        <v>22.54323694</v>
       </c>
       <c r="Q69">
-        <v>29.952306985</v>
+        <v>29.84323694</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2249324246363145</v>
+        <v>0.2298367072257005</v>
       </c>
       <c r="T69">
-        <v>1.732347453991713</v>
+        <v>1.779775614887919</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.099789076867783</v>
+        <v>4.039498061031492</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1010605463122242</v>
+        <v>0.1024756924944645</v>
       </c>
       <c r="C70">
-        <v>119.1347710308138</v>
+        <v>113.6015028783443</v>
       </c>
       <c r="D70">
-        <v>244.1457710308138</v>
+        <v>241.3082528783443</v>
       </c>
       <c r="E70">
-        <v>183.236</v>
+        <v>185.93175</v>
       </c>
       <c r="F70">
-        <v>183.311</v>
+        <v>186.00675</v>
       </c>
       <c r="G70">
         <v>58.3</v>
@@ -7021,45 +7021,45 @@
         <v>42.8</v>
       </c>
       <c r="M70">
-        <v>10.5953758</v>
+        <v>11.402213775</v>
       </c>
       <c r="N70">
-        <v>32.2046242</v>
+        <v>31.397786225</v>
       </c>
       <c r="O70">
-        <v>9.66138726</v>
+        <v>9.419335867499999</v>
       </c>
       <c r="P70">
-        <v>22.54323694</v>
+        <v>21.9784503575</v>
       </c>
       <c r="Q70">
-        <v>29.84323694</v>
+        <v>29.2784503575</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2298367072257005</v>
+        <v>0.235057395143434</v>
       </c>
       <c r="T70">
-        <v>1.779775614887919</v>
+        <v>1.830263657132268</v>
       </c>
       <c r="U70">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V70">
         <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.039498061031492</v>
+        <v>3.753657039288408</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1024756924944645</v>
+        <v>0.1022248386767049</v>
       </c>
       <c r="C71">
-        <v>113.6015028783443</v>
+        <v>111.4039218613174</v>
       </c>
       <c r="D71">
-        <v>241.3082528783443</v>
+        <v>241.8064218613174</v>
       </c>
       <c r="E71">
-        <v>185.93175</v>
+        <v>188.6275</v>
       </c>
       <c r="F71">
-        <v>186.00675</v>
+        <v>188.7025</v>
       </c>
       <c r="G71">
         <v>58.3</v>
@@ -7103,28 +7103,28 @@
         <v>42.8</v>
       </c>
       <c r="M71">
-        <v>11.402213775</v>
+        <v>11.56746325</v>
       </c>
       <c r="N71">
-        <v>31.397786225</v>
+        <v>31.23253674999999</v>
       </c>
       <c r="O71">
-        <v>9.419335867499999</v>
+        <v>9.369761024999997</v>
       </c>
       <c r="P71">
-        <v>21.9784503575</v>
+        <v>21.862775725</v>
       </c>
       <c r="Q71">
-        <v>29.2784503575</v>
+        <v>29.162775725</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.235057395143434</v>
+        <v>0.2406261289223496</v>
       </c>
       <c r="T71">
-        <v>1.830263657132268</v>
+        <v>1.884117568859573</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.753657039288408</v>
+        <v>3.700033367298573</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1022248386767049</v>
+        <v>0.1019739848589452</v>
       </c>
       <c r="C72">
-        <v>111.4039218613174</v>
+        <v>109.2084019899999</v>
       </c>
       <c r="D72">
-        <v>241.8064218613174</v>
+        <v>242.3066519899999</v>
       </c>
       <c r="E72">
-        <v>188.6275</v>
+        <v>191.32325</v>
       </c>
       <c r="F72">
-        <v>188.7025</v>
+        <v>191.39825</v>
       </c>
       <c r="G72">
         <v>58.3</v>
@@ -7185,28 +7185,28 @@
         <v>42.8</v>
       </c>
       <c r="M72">
-        <v>11.56746325</v>
+        <v>11.732712725</v>
       </c>
       <c r="N72">
-        <v>31.23253674999999</v>
+        <v>31.067287275</v>
       </c>
       <c r="O72">
-        <v>9.369761024999997</v>
+        <v>9.320186182499999</v>
       </c>
       <c r="P72">
-        <v>21.862775725</v>
+        <v>21.7471010925</v>
       </c>
       <c r="Q72">
-        <v>29.162775725</v>
+        <v>29.0471010925</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2406261289223496</v>
+        <v>0.2465789133067078</v>
       </c>
       <c r="T72">
-        <v>1.884117568859573</v>
+        <v>1.941685543464623</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.700033367298573</v>
+        <v>3.647920221280283</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1019739848589452</v>
+        <v>0.1017231310411856</v>
       </c>
       <c r="C73">
-        <v>109.2084019899999</v>
+        <v>107.0149560827184</v>
       </c>
       <c r="D73">
-        <v>242.3066519899999</v>
+        <v>242.8089560827183</v>
       </c>
       <c r="E73">
-        <v>191.32325</v>
+        <v>194.019</v>
       </c>
       <c r="F73">
-        <v>191.39825</v>
+        <v>194.094</v>
       </c>
       <c r="G73">
         <v>58.3</v>
@@ -7267,28 +7267,28 @@
         <v>42.8</v>
       </c>
       <c r="M73">
-        <v>11.732712725</v>
+        <v>11.8979622</v>
       </c>
       <c r="N73">
-        <v>31.067287275</v>
+        <v>30.9020378</v>
       </c>
       <c r="O73">
-        <v>9.320186182499999</v>
+        <v>9.270611339999999</v>
       </c>
       <c r="P73">
-        <v>21.7471010925</v>
+        <v>21.63142646</v>
       </c>
       <c r="Q73">
-        <v>29.0471010925</v>
+        <v>28.93142646</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2465789133067077</v>
+        <v>0.2529568965756628</v>
       </c>
       <c r="T73">
-        <v>1.941685543464623</v>
+        <v>2.003365516255748</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.647920221280284</v>
+        <v>3.59725466265139</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1017231310411856</v>
+        <v>0.101472277223426</v>
       </c>
       <c r="C74">
-        <v>107.0149560827184</v>
+        <v>104.82359706431</v>
       </c>
       <c r="D74">
-        <v>242.8089560827183</v>
+        <v>243.31334706431</v>
       </c>
       <c r="E74">
-        <v>194.019</v>
+        <v>196.71475</v>
       </c>
       <c r="F74">
-        <v>194.094</v>
+        <v>196.78975</v>
       </c>
       <c r="G74">
         <v>58.3</v>
@@ -7349,28 +7349,28 @@
         <v>42.8</v>
       </c>
       <c r="M74">
-        <v>11.8979622</v>
+        <v>12.063211675</v>
       </c>
       <c r="N74">
-        <v>30.9020378</v>
+        <v>30.736788325</v>
       </c>
       <c r="O74">
-        <v>9.270611339999999</v>
+        <v>9.2210364975</v>
       </c>
       <c r="P74">
-        <v>21.63142646</v>
+        <v>21.5157518275</v>
       </c>
       <c r="Q74">
-        <v>28.93142646</v>
+        <v>28.8157518275</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2529568965756628</v>
+        <v>0.2598073230497258</v>
       </c>
       <c r="T74">
-        <v>2.003365516255748</v>
+        <v>2.06961437592029</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.59725466265139</v>
+        <v>3.54797720151918</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.101472277223426</v>
+        <v>0.1012214234056663</v>
       </c>
       <c r="C75">
-        <v>104.82359706431</v>
+        <v>102.6343379672317</v>
       </c>
       <c r="D75">
-        <v>243.31334706431</v>
+        <v>243.8198379672316</v>
       </c>
       <c r="E75">
-        <v>196.71475</v>
+        <v>199.4105</v>
       </c>
       <c r="F75">
-        <v>196.78975</v>
+        <v>199.4855</v>
       </c>
       <c r="G75">
         <v>58.3</v>
@@ -7431,28 +7431,28 @@
         <v>42.8</v>
       </c>
       <c r="M75">
-        <v>12.063211675</v>
+        <v>12.22846115</v>
       </c>
       <c r="N75">
-        <v>30.736788325</v>
+        <v>30.57153885</v>
       </c>
       <c r="O75">
-        <v>9.2210364975</v>
+        <v>9.171461654999998</v>
       </c>
       <c r="P75">
-        <v>21.5157518275</v>
+        <v>21.400077195</v>
       </c>
       <c r="Q75">
-        <v>28.8157518275</v>
+        <v>28.700077195</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2598073230497258</v>
+        <v>0.2671847054064089</v>
       </c>
       <c r="T75">
-        <v>2.06961437592029</v>
+        <v>2.140959301712873</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.54797720151918</v>
+        <v>3.500031563660813</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1012214234056663</v>
+        <v>0.1024405695879067</v>
       </c>
       <c r="C76">
-        <v>102.6343379672317</v>
+        <v>97.4966296172359</v>
       </c>
       <c r="D76">
-        <v>243.8198379672316</v>
+        <v>241.3778796172359</v>
       </c>
       <c r="E76">
-        <v>199.4105</v>
+        <v>202.10625</v>
       </c>
       <c r="F76">
-        <v>199.4855</v>
+        <v>202.18125</v>
       </c>
       <c r="G76">
         <v>58.3</v>
@@ -7513,45 +7513,45 @@
         <v>42.8</v>
       </c>
       <c r="M76">
-        <v>12.22846115</v>
+        <v>12.959818125</v>
       </c>
       <c r="N76">
-        <v>30.57153885</v>
+        <v>29.840181875</v>
       </c>
       <c r="O76">
-        <v>9.171461654999998</v>
+        <v>8.952054562499999</v>
       </c>
       <c r="P76">
-        <v>21.400077195</v>
+        <v>20.8881273125</v>
       </c>
       <c r="Q76">
-        <v>28.700077195</v>
+        <v>28.1881273125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2671847054064089</v>
+        <v>0.2751522783516267</v>
       </c>
       <c r="T76">
-        <v>2.140959301712873</v>
+        <v>2.218011821568864</v>
       </c>
       <c r="U76">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.3</v>
       </c>
       <c r="W76">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.500031563660813</v>
+        <v>3.302515481867536</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1024405695879067</v>
+        <v>0.102209315770147</v>
       </c>
       <c r="C77">
-        <v>97.4966296172359</v>
+        <v>95.2603162888104</v>
       </c>
       <c r="D77">
-        <v>241.3778796172359</v>
+        <v>241.8373162888104</v>
       </c>
       <c r="E77">
-        <v>202.10625</v>
+        <v>204.802</v>
       </c>
       <c r="F77">
-        <v>202.18125</v>
+        <v>204.877</v>
       </c>
       <c r="G77">
         <v>58.3</v>
@@ -7595,28 +7595,28 @@
         <v>42.8</v>
       </c>
       <c r="M77">
-        <v>12.959818125</v>
+        <v>13.1326157</v>
       </c>
       <c r="N77">
-        <v>29.840181875</v>
+        <v>29.6673843</v>
       </c>
       <c r="O77">
-        <v>8.952054562499999</v>
+        <v>8.900215289999998</v>
       </c>
       <c r="P77">
-        <v>20.8881273125</v>
+        <v>20.76716901</v>
       </c>
       <c r="Q77">
-        <v>28.1881273125</v>
+        <v>28.06716901</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2751522783516267</v>
+        <v>0.283783815708946</v>
       </c>
       <c r="T77">
-        <v>2.218011821568864</v>
+        <v>2.301485384746187</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.302515481867536</v>
+        <v>3.259061330790332</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.102209315770147</v>
+        <v>0.1019780619523874</v>
       </c>
       <c r="C78">
-        <v>95.2603162888104</v>
+        <v>93.02575527168676</v>
       </c>
       <c r="D78">
-        <v>241.8373162888104</v>
+        <v>242.2985052716867</v>
       </c>
       <c r="E78">
-        <v>204.802</v>
+        <v>207.49775</v>
       </c>
       <c r="F78">
-        <v>204.877</v>
+        <v>207.57275</v>
       </c>
       <c r="G78">
         <v>58.3</v>
@@ -7677,28 +7677,28 @@
         <v>42.8</v>
       </c>
       <c r="M78">
-        <v>13.1326157</v>
+        <v>13.305413275</v>
       </c>
       <c r="N78">
-        <v>29.6673843</v>
+        <v>29.494586725</v>
       </c>
       <c r="O78">
-        <v>8.900215289999998</v>
+        <v>8.8483760175</v>
       </c>
       <c r="P78">
-        <v>20.76716901</v>
+        <v>20.6462107075</v>
       </c>
       <c r="Q78">
-        <v>28.06716901</v>
+        <v>27.9462107075</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.283783815708946</v>
+        <v>0.2931659215321191</v>
       </c>
       <c r="T78">
-        <v>2.301485384746187</v>
+        <v>2.392217518634581</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.259061330790332</v>
+        <v>3.216735858961886</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1019780619523874</v>
+        <v>0.1017468081346278</v>
       </c>
       <c r="C79">
-        <v>93.02575527168676</v>
+        <v>90.79295661010585</v>
       </c>
       <c r="D79">
-        <v>242.2985052716867</v>
+        <v>242.7614566101059</v>
       </c>
       <c r="E79">
-        <v>207.49775</v>
+        <v>210.1935</v>
       </c>
       <c r="F79">
-        <v>207.57275</v>
+        <v>210.2685</v>
       </c>
       <c r="G79">
         <v>58.3</v>
@@ -7759,28 +7759,28 @@
         <v>42.8</v>
       </c>
       <c r="M79">
-        <v>13.305413275</v>
+        <v>13.47821085</v>
       </c>
       <c r="N79">
-        <v>29.494586725</v>
+        <v>29.32178915</v>
       </c>
       <c r="O79">
-        <v>8.8483760175</v>
+        <v>8.796536744999999</v>
       </c>
       <c r="P79">
-        <v>20.6462107075</v>
+        <v>20.525252405</v>
       </c>
       <c r="Q79">
-        <v>27.9462107075</v>
+        <v>27.825252405</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2931659215321191</v>
+        <v>0.3034009460664899</v>
       </c>
       <c r="T79">
-        <v>2.392217518634581</v>
+        <v>2.491198028331012</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.216735858961886</v>
+        <v>3.175495655641861</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1017468081346278</v>
+        <v>0.1015155543168681</v>
       </c>
       <c r="C80">
-        <v>90.79295661010585</v>
+        <v>88.56193042522051</v>
       </c>
       <c r="D80">
-        <v>242.7614566101059</v>
+        <v>243.2261804252205</v>
       </c>
       <c r="E80">
-        <v>210.1935</v>
+        <v>212.88925</v>
       </c>
       <c r="F80">
-        <v>210.2685</v>
+        <v>212.96425</v>
       </c>
       <c r="G80">
         <v>58.3</v>
@@ -7841,28 +7841,28 @@
         <v>42.8</v>
       </c>
       <c r="M80">
-        <v>13.47821085</v>
+        <v>13.651008425</v>
       </c>
       <c r="N80">
-        <v>29.32178915</v>
+        <v>29.148991575</v>
       </c>
       <c r="O80">
-        <v>8.796536744999999</v>
+        <v>8.744697472499999</v>
       </c>
       <c r="P80">
-        <v>20.525252405</v>
+        <v>20.4042941025</v>
       </c>
       <c r="Q80">
-        <v>27.825252405</v>
+        <v>27.7042941025</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3034009460664899</v>
+        <v>0.3146107348422292</v>
       </c>
       <c r="T80">
-        <v>2.491198028331012</v>
+        <v>2.599605253236626</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.175495655641861</v>
+        <v>3.13529950810209</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1015155543168681</v>
+        <v>0.1012843004991085</v>
       </c>
       <c r="C81">
-        <v>88.56193042522051</v>
+        <v>86.33268691583251</v>
       </c>
       <c r="D81">
-        <v>243.2261804252205</v>
+        <v>243.6926869158325</v>
       </c>
       <c r="E81">
-        <v>212.88925</v>
+        <v>215.585</v>
       </c>
       <c r="F81">
-        <v>212.96425</v>
+        <v>215.66</v>
       </c>
       <c r="G81">
         <v>58.3</v>
@@ -7923,28 +7923,28 @@
         <v>42.8</v>
       </c>
       <c r="M81">
-        <v>13.651008425</v>
+        <v>13.823806</v>
       </c>
       <c r="N81">
-        <v>29.148991575</v>
+        <v>28.976194</v>
       </c>
       <c r="O81">
-        <v>8.744697472499999</v>
+        <v>8.692858199999998</v>
       </c>
       <c r="P81">
-        <v>20.4042941025</v>
+        <v>20.2833358</v>
       </c>
       <c r="Q81">
-        <v>27.7042941025</v>
+        <v>27.5833358</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3146107348422292</v>
+        <v>0.3269415024955425</v>
       </c>
       <c r="T81">
-        <v>2.599605253236626</v>
+        <v>2.718853200632801</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.13529950810209</v>
+        <v>3.096108264250814</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1012843004991085</v>
+        <v>0.1010530466813488</v>
       </c>
       <c r="C82">
-        <v>86.33268691583251</v>
+        <v>84.10523635913944</v>
       </c>
       <c r="D82">
-        <v>243.6926869158325</v>
+        <v>244.1609863591395</v>
       </c>
       <c r="E82">
-        <v>215.585</v>
+        <v>218.28075</v>
       </c>
       <c r="F82">
-        <v>215.66</v>
+        <v>218.35575</v>
       </c>
       <c r="G82">
         <v>58.3</v>
@@ -8005,28 +8005,28 @@
         <v>42.8</v>
       </c>
       <c r="M82">
-        <v>13.823806</v>
+        <v>13.996603575</v>
       </c>
       <c r="N82">
-        <v>28.976194</v>
+        <v>28.803396425</v>
       </c>
       <c r="O82">
-        <v>8.692858199999998</v>
+        <v>8.641018927499998</v>
       </c>
       <c r="P82">
-        <v>20.2833358</v>
+        <v>20.1623774975</v>
       </c>
       <c r="Q82">
-        <v>27.5833358</v>
+        <v>27.4623774975</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3269415024955425</v>
+        <v>0.3405702456913098</v>
       </c>
       <c r="T82">
-        <v>2.718853200632801</v>
+        <v>2.850653563544364</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.096108264250814</v>
+        <v>3.057884705432903</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1010530466813488</v>
+        <v>0.1008217928635892</v>
       </c>
       <c r="C83">
-        <v>84.10523635913944</v>
+        <v>81.87958911148846</v>
       </c>
       <c r="D83">
-        <v>244.1609863591395</v>
+        <v>244.6310891114885</v>
       </c>
       <c r="E83">
-        <v>218.28075</v>
+        <v>220.9765</v>
       </c>
       <c r="F83">
-        <v>218.35575</v>
+        <v>221.0515</v>
       </c>
       <c r="G83">
         <v>58.3</v>
@@ -8087,28 +8087,28 @@
         <v>42.8</v>
       </c>
       <c r="M83">
-        <v>13.996603575</v>
+        <v>14.16940115</v>
       </c>
       <c r="N83">
-        <v>28.803396425</v>
+        <v>28.63059885</v>
       </c>
       <c r="O83">
-        <v>8.641018927499998</v>
+        <v>8.589179654999999</v>
       </c>
       <c r="P83">
-        <v>20.1623774975</v>
+        <v>20.041419195</v>
       </c>
       <c r="Q83">
-        <v>27.4623774975</v>
+        <v>27.341419195</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3405702456913098</v>
+        <v>0.3557132936866068</v>
       </c>
       <c r="T83">
-        <v>2.850653563544364</v>
+        <v>2.997098411223878</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.057884705432903</v>
+        <v>3.02059342853738</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1008217928635892</v>
+        <v>0.1051223390458296</v>
       </c>
       <c r="C84">
-        <v>81.87958911148846</v>
+        <v>70.7274567346663</v>
       </c>
       <c r="D84">
-        <v>244.6310891114885</v>
+        <v>236.1747067346663</v>
       </c>
       <c r="E84">
-        <v>220.9765</v>
+        <v>223.67225</v>
       </c>
       <c r="F84">
-        <v>221.0515</v>
+        <v>223.74725</v>
       </c>
       <c r="G84">
         <v>58.3</v>
@@ -8169,45 +8169,45 @@
         <v>42.8</v>
       </c>
       <c r="M84">
-        <v>14.16940115</v>
+        <v>16.087427275</v>
       </c>
       <c r="N84">
-        <v>28.63059885</v>
+        <v>26.71257272499999</v>
       </c>
       <c r="O84">
-        <v>8.589179654999999</v>
+        <v>8.013771817499999</v>
       </c>
       <c r="P84">
-        <v>20.041419195</v>
+        <v>18.69880090749999</v>
       </c>
       <c r="Q84">
-        <v>27.341419195</v>
+        <v>25.9988009075</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3557132936866068</v>
+        <v>0.3726378767401741</v>
       </c>
       <c r="T84">
-        <v>2.997098411223878</v>
+        <v>3.160772064512746</v>
       </c>
       <c r="U84">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V84">
         <v>0.3</v>
       </c>
       <c r="W84">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>3.02059342853738</v>
+        <v>2.660462687313064</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1051223390458296</v>
+        <v>0.1049456852280699</v>
       </c>
       <c r="C85">
-        <v>70.7274567346663</v>
+        <v>68.36753935185706</v>
       </c>
       <c r="D85">
-        <v>236.1747067346663</v>
+        <v>236.5105393518571</v>
       </c>
       <c r="E85">
-        <v>223.67225</v>
+        <v>226.368</v>
       </c>
       <c r="F85">
-        <v>223.74725</v>
+        <v>226.443</v>
       </c>
       <c r="G85">
         <v>58.3</v>
@@ -8251,28 +8251,28 @@
         <v>42.8</v>
       </c>
       <c r="M85">
-        <v>16.087427275</v>
+        <v>16.2812517</v>
       </c>
       <c r="N85">
-        <v>26.71257272499999</v>
+        <v>26.5187483</v>
       </c>
       <c r="O85">
-        <v>8.013771817499999</v>
+        <v>7.955624489999998</v>
       </c>
       <c r="P85">
-        <v>18.69880090749999</v>
+        <v>18.56312381</v>
       </c>
       <c r="Q85">
-        <v>25.9988009075</v>
+        <v>25.86312381</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3726378767401741</v>
+        <v>0.3916780326754373</v>
       </c>
       <c r="T85">
-        <v>3.160772064512746</v>
+        <v>3.344904924462724</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.660462687313064</v>
+        <v>2.6287905124641</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1049456852280699</v>
+        <v>0.1047690314103103</v>
       </c>
       <c r="C86">
-        <v>68.36753935185709</v>
+        <v>66.00857841481789</v>
       </c>
       <c r="D86">
-        <v>236.5105393518571</v>
+        <v>236.8473284148179</v>
       </c>
       <c r="E86">
-        <v>226.368</v>
+        <v>229.06375</v>
       </c>
       <c r="F86">
-        <v>226.443</v>
+        <v>229.13875</v>
       </c>
       <c r="G86">
         <v>58.3</v>
@@ -8333,28 +8333,28 @@
         <v>42.8</v>
       </c>
       <c r="M86">
-        <v>16.2812517</v>
+        <v>16.475076125</v>
       </c>
       <c r="N86">
-        <v>26.5187483</v>
+        <v>26.324923875</v>
       </c>
       <c r="O86">
-        <v>7.955624489999999</v>
+        <v>7.897477162499999</v>
       </c>
       <c r="P86">
-        <v>18.56312381</v>
+        <v>18.4274467125</v>
       </c>
       <c r="Q86">
-        <v>25.86312381</v>
+        <v>25.7274467125</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.391678032675437</v>
+        <v>0.4132568760687352</v>
       </c>
       <c r="T86">
-        <v>3.344904924462722</v>
+        <v>3.553588832406029</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.6287905124641</v>
+        <v>2.59786356525864</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1047690314103103</v>
+        <v>0.1045923775925506</v>
       </c>
       <c r="C87">
-        <v>66.00857841481789</v>
+        <v>63.65057801528798</v>
       </c>
       <c r="D87">
-        <v>236.8473284148179</v>
+        <v>237.185078015288</v>
       </c>
       <c r="E87">
-        <v>229.06375</v>
+        <v>231.7595</v>
       </c>
       <c r="F87">
-        <v>229.13875</v>
+        <v>231.8345</v>
       </c>
       <c r="G87">
         <v>58.3</v>
@@ -8415,28 +8415,28 @@
         <v>42.8</v>
       </c>
       <c r="M87">
-        <v>16.475076125</v>
+        <v>16.66890055</v>
       </c>
       <c r="N87">
-        <v>26.324923875</v>
+        <v>26.13109945</v>
       </c>
       <c r="O87">
-        <v>7.897477162499999</v>
+        <v>7.839329834999999</v>
       </c>
       <c r="P87">
-        <v>18.4274467125</v>
+        <v>18.291769615</v>
       </c>
       <c r="Q87">
-        <v>25.7274467125</v>
+        <v>25.591769615</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4132568760687352</v>
+        <v>0.4379184113753617</v>
       </c>
       <c r="T87">
-        <v>3.553588832406029</v>
+        <v>3.79208472719838</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.59786356525864</v>
+        <v>2.567655849383539</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1045923775925506</v>
+        <v>0.104415723774791</v>
       </c>
       <c r="C88">
-        <v>63.65057801528798</v>
+        <v>61.29354226837964</v>
       </c>
       <c r="D88">
-        <v>237.185078015288</v>
+        <v>237.5237922683796</v>
       </c>
       <c r="E88">
-        <v>231.7595</v>
+        <v>234.45525</v>
       </c>
       <c r="F88">
-        <v>231.8345</v>
+        <v>234.53025</v>
       </c>
       <c r="G88">
         <v>58.3</v>
@@ -8497,28 +8497,28 @@
         <v>42.8</v>
       </c>
       <c r="M88">
-        <v>16.66890055</v>
+        <v>16.862724975</v>
       </c>
       <c r="N88">
-        <v>26.13109945</v>
+        <v>25.93727502499999</v>
       </c>
       <c r="O88">
-        <v>7.839329834999999</v>
+        <v>7.781182507499998</v>
       </c>
       <c r="P88">
-        <v>18.291769615</v>
+        <v>18.1560925175</v>
       </c>
       <c r="Q88">
-        <v>25.591769615</v>
+        <v>25.4560925175</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4379184113753617</v>
+        <v>0.466374029036854</v>
       </c>
       <c r="T88">
-        <v>3.79208472719838</v>
+        <v>4.067272298112631</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.567655849383539</v>
+        <v>2.538142563758441</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.104415723774791</v>
+        <v>0.1042390699570314</v>
       </c>
       <c r="C89">
-        <v>61.29354226837964</v>
+        <v>58.93747531274528</v>
       </c>
       <c r="D89">
-        <v>237.5237922683796</v>
+        <v>237.8634753127453</v>
       </c>
       <c r="E89">
-        <v>234.45525</v>
+        <v>237.151</v>
       </c>
       <c r="F89">
-        <v>234.53025</v>
+        <v>237.226</v>
       </c>
       <c r="G89">
         <v>58.3</v>
@@ -8579,28 +8579,28 @@
         <v>42.8</v>
       </c>
       <c r="M89">
-        <v>16.862724975</v>
+        <v>17.0565494</v>
       </c>
       <c r="N89">
-        <v>25.93727502499999</v>
+        <v>25.7434506</v>
       </c>
       <c r="O89">
-        <v>7.781182507499998</v>
+        <v>7.723035179999998</v>
       </c>
       <c r="P89">
-        <v>18.1560925175</v>
+        <v>18.02041542</v>
       </c>
       <c r="Q89">
-        <v>25.4560925175</v>
+        <v>25.32041542</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.466374029036854</v>
+        <v>0.4995722496419283</v>
       </c>
       <c r="T89">
-        <v>4.067272298112631</v>
+        <v>4.388324464179258</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.538142563758441</v>
+        <v>2.509300034624823</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1042390699570314</v>
+        <v>0.1064921161392717</v>
       </c>
       <c r="C90">
-        <v>58.93747531274528</v>
+        <v>51.9809206886259</v>
       </c>
       <c r="D90">
-        <v>237.8634753127453</v>
+        <v>233.6026706886259</v>
       </c>
       <c r="E90">
-        <v>237.151</v>
+        <v>239.84675</v>
       </c>
       <c r="F90">
-        <v>237.226</v>
+        <v>239.92175</v>
       </c>
       <c r="G90">
         <v>58.3</v>
@@ -8661,45 +8661,45 @@
         <v>42.8</v>
       </c>
       <c r="M90">
-        <v>17.0565494</v>
+        <v>18.18606865</v>
       </c>
       <c r="N90">
-        <v>25.7434506</v>
+        <v>24.61393134999999</v>
       </c>
       <c r="O90">
-        <v>7.723035179999998</v>
+        <v>7.384179404999998</v>
       </c>
       <c r="P90">
-        <v>18.02041542</v>
+        <v>17.229751945</v>
       </c>
       <c r="Q90">
-        <v>25.32041542</v>
+        <v>24.529751945</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4995722496419283</v>
+        <v>0.5388065103570159</v>
       </c>
       <c r="T90">
-        <v>4.388324464179258</v>
+        <v>4.767749751348908</v>
       </c>
       <c r="U90">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V90">
         <v>0.3</v>
       </c>
       <c r="W90">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.509300034624823</v>
+        <v>2.353449820503124</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1064921161392717</v>
+        <v>0.1063427623215121</v>
       </c>
       <c r="C91">
-        <v>51.9809206886259</v>
+        <v>49.56288860736726</v>
       </c>
       <c r="D91">
-        <v>233.6026706886259</v>
+        <v>233.8803886073673</v>
       </c>
       <c r="E91">
-        <v>239.84675</v>
+        <v>242.5425</v>
       </c>
       <c r="F91">
-        <v>239.92175</v>
+        <v>242.6175</v>
       </c>
       <c r="G91">
         <v>58.3</v>
@@ -8743,28 +8743,28 @@
         <v>42.8</v>
       </c>
       <c r="M91">
-        <v>18.18606865</v>
+        <v>18.3904065</v>
       </c>
       <c r="N91">
-        <v>24.61393134999999</v>
+        <v>24.4095935</v>
       </c>
       <c r="O91">
-        <v>7.384179404999998</v>
+        <v>7.322878049999998</v>
       </c>
       <c r="P91">
-        <v>17.229751945</v>
+        <v>17.08671545</v>
       </c>
       <c r="Q91">
-        <v>24.529751945</v>
+        <v>24.38671545</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5388065103570159</v>
+        <v>0.585887623215121</v>
       </c>
       <c r="T91">
-        <v>4.767749751348908</v>
+        <v>5.223060095952487</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.353449820503124</v>
+        <v>2.327300378053089</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1063427623215121</v>
+        <v>0.1061934085037524</v>
       </c>
       <c r="C92">
-        <v>49.56288860736726</v>
+        <v>47.14551764050273</v>
       </c>
       <c r="D92">
-        <v>233.8803886073673</v>
+        <v>234.1587676405028</v>
       </c>
       <c r="E92">
-        <v>242.5425</v>
+        <v>245.23825</v>
       </c>
       <c r="F92">
-        <v>242.6175</v>
+        <v>245.31325</v>
       </c>
       <c r="G92">
         <v>58.3</v>
@@ -8825,28 +8825,28 @@
         <v>42.8</v>
       </c>
       <c r="M92">
-        <v>18.3904065</v>
+        <v>18.59474435</v>
       </c>
       <c r="N92">
-        <v>24.4095935</v>
+        <v>24.20525564999999</v>
       </c>
       <c r="O92">
-        <v>7.322878049999998</v>
+        <v>7.261576694999998</v>
       </c>
       <c r="P92">
-        <v>17.08671545</v>
+        <v>16.943678955</v>
       </c>
       <c r="Q92">
-        <v>24.38671545</v>
+        <v>24.243678955</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.585887623215121</v>
+        <v>0.6434312055972496</v>
       </c>
       <c r="T92">
-        <v>5.223060095952487</v>
+        <v>5.77955051713464</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.327300378053089</v>
+        <v>2.301725648623934</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1061934085037524</v>
+        <v>0.1060440546859928</v>
       </c>
       <c r="C93">
-        <v>47.14551764050273</v>
+        <v>44.72881015154437</v>
       </c>
       <c r="D93">
-        <v>234.1587676405028</v>
+        <v>234.4378101515443</v>
       </c>
       <c r="E93">
-        <v>245.23825</v>
+        <v>247.934</v>
       </c>
       <c r="F93">
-        <v>245.31325</v>
+        <v>248.009</v>
       </c>
       <c r="G93">
         <v>58.3</v>
@@ -8907,28 +8907,28 @@
         <v>42.8</v>
       </c>
       <c r="M93">
-        <v>18.59474435</v>
+        <v>18.7990822</v>
       </c>
       <c r="N93">
-        <v>24.20525564999999</v>
+        <v>24.0009178</v>
       </c>
       <c r="O93">
-        <v>7.261576694999998</v>
+        <v>7.200275339999998</v>
       </c>
       <c r="P93">
-        <v>16.943678955</v>
+        <v>16.80064246</v>
       </c>
       <c r="Q93">
-        <v>24.243678955</v>
+        <v>24.10064246</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6434312055972496</v>
+        <v>0.7153606835749106</v>
       </c>
       <c r="T93">
-        <v>5.77955051713464</v>
+        <v>6.475163543612331</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.301725648623934</v>
+        <v>2.276706891573674</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1060440546859928</v>
+        <v>0.1058947008682332</v>
       </c>
       <c r="C94">
-        <v>44.72881015154437</v>
+        <v>42.31276851528366</v>
       </c>
       <c r="D94">
-        <v>234.4378101515443</v>
+        <v>234.7175185152837</v>
       </c>
       <c r="E94">
-        <v>247.934</v>
+        <v>250.62975</v>
       </c>
       <c r="F94">
-        <v>248.009</v>
+        <v>250.70475</v>
       </c>
       <c r="G94">
         <v>58.3</v>
@@ -8989,28 +8989,28 @@
         <v>42.8</v>
       </c>
       <c r="M94">
-        <v>18.7990822</v>
+        <v>19.00342005</v>
       </c>
       <c r="N94">
-        <v>24.0009178</v>
+        <v>23.79657994999999</v>
       </c>
       <c r="O94">
-        <v>7.200275339999998</v>
+        <v>7.138973984999998</v>
       </c>
       <c r="P94">
-        <v>16.80064246</v>
+        <v>16.65760596499999</v>
       </c>
       <c r="Q94">
-        <v>24.10064246</v>
+        <v>23.957605965</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7153606835749106</v>
+        <v>0.8078414409747602</v>
       </c>
       <c r="T94">
-        <v>6.475163543612331</v>
+        <v>7.369523149083649</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.276706891573674</v>
+        <v>2.252226172309441</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1058947008682332</v>
+        <v>0.1057453470504735</v>
       </c>
       <c r="C95">
-        <v>42.31276851528366</v>
+        <v>39.89739511785953</v>
       </c>
       <c r="D95">
-        <v>234.7175185152837</v>
+        <v>234.9978951178595</v>
       </c>
       <c r="E95">
-        <v>250.62975</v>
+        <v>253.3255</v>
       </c>
       <c r="F95">
-        <v>250.70475</v>
+        <v>253.4005</v>
       </c>
       <c r="G95">
         <v>58.3</v>
@@ -9071,28 +9071,28 @@
         <v>42.8</v>
       </c>
       <c r="M95">
-        <v>19.00342005</v>
+        <v>19.2077579</v>
       </c>
       <c r="N95">
-        <v>23.79657994999999</v>
+        <v>23.5922421</v>
       </c>
       <c r="O95">
-        <v>7.138973984999998</v>
+        <v>7.077672629999999</v>
       </c>
       <c r="P95">
-        <v>16.65760596499999</v>
+        <v>16.51456947</v>
       </c>
       <c r="Q95">
-        <v>23.957605965</v>
+        <v>23.81456947</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8078414409747602</v>
+        <v>0.9311491175078931</v>
       </c>
       <c r="T95">
-        <v>7.369523149083649</v>
+        <v>8.562002623045407</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.252226172309441</v>
+        <v>2.228266319412533</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1057453470504735</v>
+        <v>0.1055959932327139</v>
       </c>
       <c r="C96">
-        <v>39.89739511785953</v>
+        <v>37.48269235682545</v>
       </c>
       <c r="D96">
-        <v>234.9978951178595</v>
+        <v>235.2789423568254</v>
       </c>
       <c r="E96">
-        <v>253.3255</v>
+        <v>256.02125</v>
       </c>
       <c r="F96">
-        <v>253.4005</v>
+        <v>256.09625</v>
       </c>
       <c r="G96">
         <v>58.3</v>
@@ -9153,28 +9153,28 @@
         <v>42.8</v>
       </c>
       <c r="M96">
-        <v>19.2077579</v>
+        <v>19.41209575</v>
       </c>
       <c r="N96">
-        <v>23.5922421</v>
+        <v>23.38790424999999</v>
       </c>
       <c r="O96">
-        <v>7.077672629999999</v>
+        <v>7.016371274999998</v>
       </c>
       <c r="P96">
-        <v>16.51456947</v>
+        <v>16.371532975</v>
       </c>
       <c r="Q96">
-        <v>23.81456947</v>
+        <v>23.671532975</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9311491175078931</v>
+        <v>1.10377986465428</v>
       </c>
       <c r="T96">
-        <v>8.562002623045407</v>
+        <v>10.23147388659187</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.228266319412533</v>
+        <v>2.204810884471348</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1055959932327139</v>
+        <v>0.1054466394149543</v>
       </c>
       <c r="C97">
-        <v>37.48269235682545</v>
+        <v>35.06866264121805</v>
       </c>
       <c r="D97">
-        <v>235.2789423568254</v>
+        <v>235.5606626412181</v>
       </c>
       <c r="E97">
-        <v>256.02125</v>
+        <v>258.717</v>
       </c>
       <c r="F97">
-        <v>256.09625</v>
+        <v>258.792</v>
       </c>
       <c r="G97">
         <v>58.3</v>
@@ -9235,28 +9235,28 @@
         <v>42.8</v>
       </c>
       <c r="M97">
-        <v>19.41209575</v>
+        <v>19.6164336</v>
       </c>
       <c r="N97">
-        <v>23.38790424999999</v>
+        <v>23.18356639999999</v>
       </c>
       <c r="O97">
-        <v>7.016371274999998</v>
+        <v>6.955069919999998</v>
       </c>
       <c r="P97">
-        <v>16.371532975</v>
+        <v>16.22849648</v>
       </c>
       <c r="Q97">
-        <v>23.671532975</v>
+        <v>23.52849648</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.10377986465428</v>
+        <v>1.362725985373859</v>
       </c>
       <c r="T97">
-        <v>10.23147388659187</v>
+        <v>12.73568078191157</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.204810884471348</v>
+        <v>2.181844104424771</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1054466394149543</v>
+        <v>0.1052972855971946</v>
       </c>
       <c r="C98">
-        <v>35.06866264121811</v>
+        <v>32.65530839162642</v>
       </c>
       <c r="D98">
-        <v>235.5606626412181</v>
+        <v>235.8430583916264</v>
       </c>
       <c r="E98">
-        <v>258.717</v>
+        <v>261.41275</v>
       </c>
       <c r="F98">
-        <v>258.792</v>
+        <v>261.48775</v>
       </c>
       <c r="G98">
         <v>58.3</v>
@@ -9317,28 +9317,28 @@
         <v>42.8</v>
       </c>
       <c r="M98">
-        <v>19.6164336</v>
+        <v>19.82077145</v>
       </c>
       <c r="N98">
-        <v>23.1835664</v>
+        <v>22.97922854999999</v>
       </c>
       <c r="O98">
-        <v>6.955069919999999</v>
+        <v>6.893768564999998</v>
       </c>
       <c r="P98">
-        <v>16.22849648</v>
+        <v>16.085459985</v>
       </c>
       <c r="Q98">
-        <v>23.52849648</v>
+        <v>23.385459985</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.362725985373856</v>
+        <v>1.79430285323982</v>
       </c>
       <c r="T98">
-        <v>12.73568078191153</v>
+        <v>16.90935894077767</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.181844104424771</v>
+        <v>2.159350866234825</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1052972855971946</v>
+        <v>0.105147931779435</v>
       </c>
       <c r="C99">
-        <v>32.65530839162642</v>
+        <v>30.24263204026062</v>
       </c>
       <c r="D99">
-        <v>235.8430583916264</v>
+        <v>236.1261320402606</v>
       </c>
       <c r="E99">
-        <v>261.41275</v>
+        <v>264.1085</v>
       </c>
       <c r="F99">
-        <v>261.48775</v>
+        <v>264.1835</v>
       </c>
       <c r="G99">
         <v>58.3</v>
@@ -9399,28 +9399,28 @@
         <v>42.8</v>
       </c>
       <c r="M99">
-        <v>19.82077145</v>
+        <v>20.0251093</v>
       </c>
       <c r="N99">
-        <v>22.97922854999999</v>
+        <v>22.7748907</v>
       </c>
       <c r="O99">
-        <v>6.893768564999998</v>
+        <v>6.832467209999999</v>
       </c>
       <c r="P99">
-        <v>16.085459985</v>
+        <v>15.94242349</v>
       </c>
       <c r="Q99">
-        <v>23.385459985</v>
+        <v>23.24242349</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.79430285323982</v>
+        <v>2.657456588971747</v>
       </c>
       <c r="T99">
-        <v>16.90935894077767</v>
+        <v>25.25671525850995</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.159350866234825</v>
+        <v>2.137316673722225</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.105147931779435</v>
+        <v>0.1049985779616754</v>
       </c>
       <c r="C100">
-        <v>30.24263204026062</v>
+        <v>27.83063603102192</v>
       </c>
       <c r="D100">
-        <v>236.1261320402606</v>
+        <v>236.4098860310219</v>
       </c>
       <c r="E100">
-        <v>264.1085</v>
+        <v>266.80425</v>
       </c>
       <c r="F100">
-        <v>264.1835</v>
+        <v>266.87925</v>
       </c>
       <c r="G100">
         <v>58.3</v>
@@ -9481,28 +9481,28 @@
         <v>42.8</v>
       </c>
       <c r="M100">
-        <v>20.0251093</v>
+        <v>20.22944715</v>
       </c>
       <c r="N100">
-        <v>22.7748907</v>
+        <v>22.57055285</v>
       </c>
       <c r="O100">
-        <v>6.832467209999999</v>
+        <v>6.771165854999999</v>
       </c>
       <c r="P100">
-        <v>15.94242349</v>
+        <v>15.799386995</v>
       </c>
       <c r="Q100">
-        <v>23.24242349</v>
+        <v>23.099386995</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.657456588971747</v>
+        <v>5.24691779616753</v>
       </c>
       <c r="T100">
-        <v>25.25671525850995</v>
+        <v>50.29878421170677</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.137316673722225</v>
+        <v>2.115727616411899</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1049985779616754</v>
-      </c>
-      <c r="C101">
-        <v>27.83063603102192</v>
-      </c>
-      <c r="D101">
-        <v>236.4098860310219</v>
-      </c>
-      <c r="E101">
-        <v>266.80425</v>
-      </c>
-      <c r="F101">
-        <v>266.87925</v>
-      </c>
-      <c r="G101">
-        <v>58.3</v>
-      </c>
-      <c r="H101">
-        <v>269.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>50.1</v>
-      </c>
-      <c r="K101">
-        <v>7.300000000000004</v>
-      </c>
-      <c r="L101">
-        <v>42.8</v>
-      </c>
-      <c r="M101">
-        <v>20.22944715</v>
-      </c>
-      <c r="N101">
-        <v>22.57055285</v>
-      </c>
-      <c r="O101">
-        <v>6.771165854999999</v>
-      </c>
-      <c r="P101">
-        <v>15.799386995</v>
-      </c>
-      <c r="Q101">
-        <v>23.099386995</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.24691779616753</v>
-      </c>
-      <c r="T101">
-        <v>50.29878421170677</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.05306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.115727616411899</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
